--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113245476</v>
+        <v>113245616</v>
       </c>
       <c r="B43" t="n">
-        <v>90488</v>
+        <v>90492</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,21 +6165,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5467</v>
+        <v>1213</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113244725</v>
+        <v>113246509</v>
       </c>
       <c r="B44" t="n">
-        <v>90776</v>
+        <v>55984</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6291,34 +6291,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1975</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6326,10 +6335,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317004</v>
+        <v>316984</v>
       </c>
       <c r="R44" t="n">
-        <v>6566831</v>
+        <v>6566956</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6370,28 +6379,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6409,10 +6402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113252817</v>
+        <v>113244003</v>
       </c>
       <c r="B45" t="n">
-        <v>89954</v>
+        <v>91494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6425,28 +6418,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6460,10 +6449,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>316989</v>
+        <v>316970</v>
       </c>
       <c r="R45" t="n">
-        <v>6567074</v>
+        <v>6566774</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6525,7 +6514,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6543,10 +6532,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113246404</v>
+        <v>113244952</v>
       </c>
       <c r="B46" t="n">
-        <v>55976</v>
+        <v>91329</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6559,21 +6548,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6581,13 +6570,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6595,10 +6583,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316961</v>
+        <v>317047</v>
       </c>
       <c r="R46" t="n">
-        <v>6566845</v>
+        <v>6567067</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6639,12 +6627,13 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6662,10 +6651,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113246470</v>
+        <v>113246404</v>
       </c>
       <c r="B47" t="n">
-        <v>56910</v>
+        <v>55976</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6678,35 +6667,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6714,10 +6703,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317031</v>
+        <v>316961</v>
       </c>
       <c r="R47" t="n">
-        <v>6567009</v>
+        <v>6566845</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6752,11 +6741,6 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6768,7 +6752,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6786,10 +6770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113243787</v>
+        <v>113245476</v>
       </c>
       <c r="B48" t="n">
-        <v>90040</v>
+        <v>90504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6798,32 +6782,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>5467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6837,10 +6817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316816</v>
+        <v>316848</v>
       </c>
       <c r="R48" t="n">
-        <v>6566787</v>
+        <v>6567253</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6892,17 +6872,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6920,10 +6900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113246434</v>
+        <v>113244505</v>
       </c>
       <c r="B49" t="n">
-        <v>56765</v>
+        <v>89127</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6936,39 +6916,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6976,10 +6947,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>317072</v>
+        <v>316987</v>
       </c>
       <c r="R49" t="n">
-        <v>6566964</v>
+        <v>6566830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7020,27 +6991,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7058,10 +7030,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113245823</v>
+        <v>113246434</v>
       </c>
       <c r="B50" t="n">
-        <v>90634</v>
+        <v>56765</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7074,30 +7046,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5454</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7105,10 +7086,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316794</v>
+        <v>317072</v>
       </c>
       <c r="R50" t="n">
-        <v>6567127</v>
+        <v>6566964</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7149,7 +7130,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7160,17 +7140,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7188,10 +7168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113245616</v>
+        <v>113244725</v>
       </c>
       <c r="B51" t="n">
-        <v>90476</v>
+        <v>90792</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7200,25 +7180,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1213</v>
+        <v>1975</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7235,10 +7215,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>316848</v>
+        <v>317004</v>
       </c>
       <c r="R51" t="n">
-        <v>6567253</v>
+        <v>6566831</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7285,7 +7265,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7318,10 +7298,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113244782</v>
+        <v>113244911</v>
       </c>
       <c r="B52" t="n">
-        <v>89111</v>
+        <v>90045</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7334,21 +7314,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7365,10 +7345,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316904</v>
+        <v>316924</v>
       </c>
       <c r="R52" t="n">
-        <v>6567084</v>
+        <v>6567085</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7415,22 +7395,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7448,10 +7428,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113246509</v>
+        <v>113245823</v>
       </c>
       <c r="B53" t="n">
-        <v>55984</v>
+        <v>90650</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7460,43 +7440,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>5454</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7504,10 +7475,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316984</v>
+        <v>316794</v>
       </c>
       <c r="R53" t="n">
-        <v>6566956</v>
+        <v>6567127</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7548,12 +7519,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7571,10 +7558,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244911</v>
+        <v>113244782</v>
       </c>
       <c r="B54" t="n">
-        <v>90029</v>
+        <v>89127</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7587,21 +7574,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7618,10 +7605,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316924</v>
+        <v>316904</v>
       </c>
       <c r="R54" t="n">
-        <v>6567085</v>
+        <v>6567084</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7668,22 +7655,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7701,10 +7688,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113245002</v>
+        <v>113252817</v>
       </c>
       <c r="B55" t="n">
-        <v>89111</v>
+        <v>89970</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7717,24 +7704,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7748,10 +7739,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317012</v>
+        <v>316989</v>
       </c>
       <c r="R55" t="n">
-        <v>6566822</v>
+        <v>6567074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7798,7 +7789,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7813,7 +7804,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7831,10 +7822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113244505</v>
+        <v>113245002</v>
       </c>
       <c r="B56" t="n">
-        <v>89111</v>
+        <v>89127</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7878,10 +7869,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316987</v>
+        <v>317012</v>
       </c>
       <c r="R56" t="n">
-        <v>6566830</v>
+        <v>6566822</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7961,10 +7952,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113244003</v>
+        <v>113243787</v>
       </c>
       <c r="B57" t="n">
-        <v>91478</v>
+        <v>90056</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7973,28 +7964,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8008,10 +8003,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316970</v>
+        <v>316816</v>
       </c>
       <c r="R57" t="n">
-        <v>6566774</v>
+        <v>6566787</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8063,17 +8058,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8091,10 +8086,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113244952</v>
+        <v>113246470</v>
       </c>
       <c r="B58" t="n">
-        <v>91313</v>
+        <v>56910</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8107,34 +8102,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8142,10 +8138,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317047</v>
+        <v>317031</v>
       </c>
       <c r="R58" t="n">
-        <v>6567067</v>
+        <v>6567009</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8180,13 +8176,17 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B59" t="n">
-        <v>8432</v>
+        <v>90264</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,36 +8222,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8259,10 +8257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R59" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8342,10 +8340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B60" t="n">
-        <v>90248</v>
+        <v>8432</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8354,34 +8352,36 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R60" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335725</v>
+        <v>113335687</v>
       </c>
       <c r="B61" t="n">
-        <v>89604</v>
+        <v>89127</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>937</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317054</v>
+        <v>317131</v>
       </c>
       <c r="R61" t="n">
-        <v>6566709</v>
+        <v>6566427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,22 +8569,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113336300</v>
+        <v>113335903</v>
       </c>
       <c r="B62" t="n">
-        <v>89954</v>
+        <v>91494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317034</v>
+        <v>317062</v>
       </c>
       <c r="R62" t="n">
-        <v>6566659</v>
+        <v>6566632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113335687</v>
+        <v>113335725</v>
       </c>
       <c r="B63" t="n">
-        <v>89111</v>
+        <v>89620</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>937</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317131</v>
+        <v>317054</v>
       </c>
       <c r="R63" t="n">
-        <v>6566427</v>
+        <v>6566709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8829,22 +8829,22 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335903</v>
+        <v>113336300</v>
       </c>
       <c r="B64" t="n">
-        <v>91478</v>
+        <v>89970</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317062</v>
+        <v>317034</v>
       </c>
       <c r="R64" t="n">
-        <v>6566632</v>
+        <v>6566659</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B65" t="n">
-        <v>78105</v>
+        <v>55984</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,34 +9004,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9039,10 +9048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R65" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9083,28 +9092,12 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9122,10 +9115,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338164</v>
+        <v>113338079</v>
       </c>
       <c r="B66" t="n">
-        <v>55984</v>
+        <v>56765</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9134,41 +9127,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9178,10 +9163,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317128</v>
+        <v>317148</v>
       </c>
       <c r="R66" t="n">
-        <v>6566863</v>
+        <v>6566451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9228,6 +9213,21 @@
       <c r="AI66" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338079</v>
+        <v>113338739</v>
       </c>
       <c r="B67" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9261,31 +9261,30 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9293,10 +9292,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317148</v>
+        <v>317102</v>
       </c>
       <c r="R67" t="n">
-        <v>6566451</v>
+        <v>6566586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9337,27 +9336,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378411</v>
+        <v>113378087</v>
       </c>
       <c r="B68" t="n">
-        <v>4990</v>
+        <v>90650</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,32 +9391,30 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>105212</v>
+        <v>5454</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9424,10 +9422,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316861</v>
+        <v>316719</v>
       </c>
       <c r="R68" t="n">
-        <v>6566893</v>
+        <v>6566788</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9479,17 +9477,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9507,10 +9505,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113377981</v>
+        <v>113378820</v>
       </c>
       <c r="B69" t="n">
-        <v>90289</v>
+        <v>94870</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9523,30 +9521,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9554,10 +9553,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316671</v>
+        <v>316796</v>
       </c>
       <c r="R69" t="n">
-        <v>6566772</v>
+        <v>6567088</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9601,26 +9600,6 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9637,10 +9616,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378715</v>
+        <v>113378364</v>
       </c>
       <c r="B70" t="n">
-        <v>90248</v>
+        <v>94870</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9649,34 +9628,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9684,10 +9664,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316843</v>
+        <v>316813</v>
       </c>
       <c r="R70" t="n">
-        <v>6567058</v>
+        <v>6566808</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9749,7 +9729,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9767,10 +9747,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378035</v>
+        <v>113377981</v>
       </c>
       <c r="B71" t="n">
-        <v>94854</v>
+        <v>90305</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9783,31 +9763,30 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9815,10 +9794,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316688</v>
+        <v>316671</v>
       </c>
       <c r="R71" t="n">
-        <v>6566808</v>
+        <v>6566772</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9870,17 +9849,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9898,10 +9877,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113378820</v>
+        <v>113378774</v>
       </c>
       <c r="B72" t="n">
-        <v>94854</v>
+        <v>94870</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9946,10 +9925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316796</v>
+        <v>316837</v>
       </c>
       <c r="R72" t="n">
-        <v>6567088</v>
+        <v>6566820</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9993,6 +9972,26 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -10009,10 +10008,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378087</v>
+        <v>113377913</v>
       </c>
       <c r="B73" t="n">
-        <v>90634</v>
+        <v>94870</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10025,30 +10024,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5454</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316719</v>
+        <v>316859</v>
       </c>
       <c r="R73" t="n">
-        <v>6566788</v>
+        <v>6566682</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10111,17 +10111,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10139,10 +10139,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113377913</v>
+        <v>113378035</v>
       </c>
       <c r="B74" t="n">
-        <v>94854</v>
+        <v>94870</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10187,10 +10187,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316859</v>
+        <v>316688</v>
       </c>
       <c r="R74" t="n">
-        <v>6566682</v>
+        <v>6566808</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10242,17 +10242,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10270,10 +10270,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378172</v>
+        <v>113377902</v>
       </c>
       <c r="B75" t="n">
-        <v>89604</v>
+        <v>94870</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10286,30 +10286,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10317,10 +10318,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316763</v>
+        <v>316879</v>
       </c>
       <c r="R75" t="n">
-        <v>6566812</v>
+        <v>6566606</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10372,17 +10373,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10400,10 +10401,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378364</v>
+        <v>113378352</v>
       </c>
       <c r="B76" t="n">
-        <v>94854</v>
+        <v>5163</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10416,31 +10417,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10448,10 +10450,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316813</v>
+        <v>316796</v>
       </c>
       <c r="R76" t="n">
-        <v>6566808</v>
+        <v>6566783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10503,17 +10505,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10531,10 +10533,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378352</v>
+        <v>113378411</v>
       </c>
       <c r="B77" t="n">
-        <v>5163</v>
+        <v>4990</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10547,21 +10549,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102204</v>
+        <v>105212</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10580,10 +10582,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316796</v>
+        <v>316861</v>
       </c>
       <c r="R77" t="n">
-        <v>6566783</v>
+        <v>6566893</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10645,7 +10647,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10663,10 +10665,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113377902</v>
+        <v>113378172</v>
       </c>
       <c r="B78" t="n">
-        <v>94854</v>
+        <v>89620</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10679,31 +10681,30 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>937</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10711,10 +10712,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316879</v>
+        <v>316763</v>
       </c>
       <c r="R78" t="n">
-        <v>6566606</v>
+        <v>6566812</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10766,17 +10767,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10794,10 +10795,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378774</v>
+        <v>113378715</v>
       </c>
       <c r="B79" t="n">
-        <v>94854</v>
+        <v>90264</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10806,35 +10807,34 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316837</v>
+        <v>316843</v>
       </c>
       <c r="R79" t="n">
-        <v>6566820</v>
+        <v>6567058</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90248</v>
+        <v>90264</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427288</v>
+        <v>113427239</v>
       </c>
       <c r="B81" t="n">
-        <v>90248</v>
+        <v>90504</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5260</v>
+        <v>5467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316863</v>
+        <v>316795</v>
       </c>
       <c r="R81" t="n">
-        <v>6567163</v>
+        <v>6567015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113427359</v>
+        <v>113405650</v>
       </c>
       <c r="B82" t="n">
-        <v>94854</v>
+        <v>43540</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11197,35 +11197,36 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11233,10 +11234,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316843</v>
+        <v>316574</v>
       </c>
       <c r="R82" t="n">
-        <v>6567130</v>
+        <v>6566830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11263,12 +11264,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11283,22 +11284,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11316,10 +11317,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113406315</v>
+        <v>113405679</v>
       </c>
       <c r="B83" t="n">
-        <v>89954</v>
+        <v>43540</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11328,38 +11329,36 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11367,10 +11366,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316935</v>
+        <v>316567</v>
       </c>
       <c r="R83" t="n">
-        <v>6566886</v>
+        <v>6566848</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11417,22 +11416,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11450,10 +11449,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113405679</v>
+        <v>113427359</v>
       </c>
       <c r="B84" t="n">
-        <v>43540</v>
+        <v>94870</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11462,36 +11461,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11499,10 +11497,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316567</v>
+        <v>316843</v>
       </c>
       <c r="R84" t="n">
-        <v>6566848</v>
+        <v>6567130</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11529,12 +11527,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11549,22 +11547,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11582,10 +11580,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427239</v>
+        <v>113427288</v>
       </c>
       <c r="B85" t="n">
-        <v>90488</v>
+        <v>90264</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11594,25 +11592,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5467</v>
+        <v>5260</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11629,10 +11627,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316795</v>
+        <v>316863</v>
       </c>
       <c r="R85" t="n">
-        <v>6567015</v>
+        <v>6567163</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11712,10 +11710,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113405650</v>
+        <v>113406315</v>
       </c>
       <c r="B86" t="n">
-        <v>43540</v>
+        <v>89970</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11724,36 +11722,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316574</v>
+        <v>316935</v>
       </c>
       <c r="R86" t="n">
-        <v>6566830</v>
+        <v>6566886</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11811,22 +11811,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B90" t="n">
-        <v>90182</v>
+        <v>89620</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R90" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,6 +12328,26 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12344,10 +12364,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B91" t="n">
-        <v>89604</v>
+        <v>90198</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12356,25 +12376,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12391,10 +12411,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R91" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12438,26 +12458,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90476</v>
+        <v>90492</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90431</v>
+        <v>90447</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -11449,10 +11449,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427359</v>
+        <v>113427288</v>
       </c>
       <c r="B84" t="n">
-        <v>94870</v>
+        <v>90264</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11461,35 +11461,34 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11497,10 +11496,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316843</v>
+        <v>316863</v>
       </c>
       <c r="R84" t="n">
-        <v>6567130</v>
+        <v>6567163</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11580,10 +11579,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427288</v>
+        <v>113427359</v>
       </c>
       <c r="B85" t="n">
-        <v>90264</v>
+        <v>94870</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11592,34 +11591,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11627,10 +11627,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316863</v>
+        <v>316843</v>
       </c>
       <c r="R85" t="n">
-        <v>6567163</v>
+        <v>6567130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113245616</v>
+        <v>113252817</v>
       </c>
       <c r="B43" t="n">
-        <v>90492</v>
+        <v>89970</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,24 +6165,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1213</v>
+        <v>3242</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6196,10 +6200,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316848</v>
+        <v>316989</v>
       </c>
       <c r="R43" t="n">
-        <v>6567253</v>
+        <v>6567074</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6261,7 +6265,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6532,10 +6536,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113244952</v>
+        <v>113245823</v>
       </c>
       <c r="B46" t="n">
-        <v>91329</v>
+        <v>90650</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6548,28 +6552,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5454</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>317047</v>
+        <v>316794</v>
       </c>
       <c r="R46" t="n">
-        <v>6567067</v>
+        <v>6567127</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6634,6 +6634,21 @@
       <c r="AI46" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6651,10 +6666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113246404</v>
+        <v>113245002</v>
       </c>
       <c r="B47" t="n">
-        <v>55976</v>
+        <v>89127</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6667,35 +6682,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6703,10 +6713,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316961</v>
+        <v>317012</v>
       </c>
       <c r="R47" t="n">
-        <v>6566845</v>
+        <v>6566822</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6747,12 +6757,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6770,10 +6796,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113245476</v>
+        <v>113243787</v>
       </c>
       <c r="B48" t="n">
-        <v>90504</v>
+        <v>90056</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6782,28 +6808,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5467</v>
+        <v>1205</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6817,10 +6847,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316848</v>
+        <v>316816</v>
       </c>
       <c r="R48" t="n">
-        <v>6567253</v>
+        <v>6566787</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6872,17 +6902,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6900,10 +6930,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244505</v>
+        <v>113244911</v>
       </c>
       <c r="B49" t="n">
-        <v>89127</v>
+        <v>90045</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6916,21 +6946,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6947,10 +6977,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316987</v>
+        <v>316924</v>
       </c>
       <c r="R49" t="n">
-        <v>6566830</v>
+        <v>6567085</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6997,22 +7027,22 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7030,10 +7060,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113246434</v>
+        <v>113245476</v>
       </c>
       <c r="B50" t="n">
-        <v>56765</v>
+        <v>90504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7046,39 +7076,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5467</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7086,10 +7107,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>317072</v>
+        <v>316848</v>
       </c>
       <c r="R50" t="n">
-        <v>6566964</v>
+        <v>6567253</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7130,6 +7151,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7140,17 +7162,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7298,10 +7320,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113244911</v>
+        <v>113246470</v>
       </c>
       <c r="B52" t="n">
-        <v>90045</v>
+        <v>56910</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7314,30 +7336,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7345,10 +7372,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316924</v>
+        <v>317031</v>
       </c>
       <c r="R52" t="n">
-        <v>6567085</v>
+        <v>6567009</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7383,34 +7410,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Låga # Picea abies</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7428,10 +7444,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113245823</v>
+        <v>113245616</v>
       </c>
       <c r="B53" t="n">
-        <v>90650</v>
+        <v>90492</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7444,21 +7460,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5454</v>
+        <v>1213</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7475,10 +7491,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316794</v>
+        <v>316848</v>
       </c>
       <c r="R53" t="n">
-        <v>6567127</v>
+        <v>6567253</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7558,10 +7574,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244782</v>
+        <v>113246434</v>
       </c>
       <c r="B54" t="n">
-        <v>89127</v>
+        <v>56765</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7574,30 +7590,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7605,10 +7630,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316904</v>
+        <v>317072</v>
       </c>
       <c r="R54" t="n">
-        <v>6567084</v>
+        <v>6566964</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7649,7 +7674,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7660,17 +7684,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7688,10 +7712,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113252817</v>
+        <v>113244505</v>
       </c>
       <c r="B55" t="n">
-        <v>89970</v>
+        <v>89127</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7704,28 +7728,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7739,10 +7759,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316989</v>
+        <v>316987</v>
       </c>
       <c r="R55" t="n">
-        <v>6567074</v>
+        <v>6566830</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7789,7 +7809,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7804,7 +7824,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7822,10 +7842,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113245002</v>
+        <v>113246404</v>
       </c>
       <c r="B56" t="n">
-        <v>89127</v>
+        <v>55976</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7838,30 +7858,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7869,10 +7894,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317012</v>
+        <v>316961</v>
       </c>
       <c r="R56" t="n">
-        <v>6566822</v>
+        <v>6566845</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7913,28 +7938,12 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7952,10 +7961,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113243787</v>
+        <v>113244782</v>
       </c>
       <c r="B57" t="n">
-        <v>90056</v>
+        <v>89127</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7964,32 +7973,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8003,10 +8008,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316816</v>
+        <v>316904</v>
       </c>
       <c r="R57" t="n">
-        <v>6566787</v>
+        <v>6567084</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8058,17 +8063,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8086,10 +8091,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113246470</v>
+        <v>113244952</v>
       </c>
       <c r="B58" t="n">
-        <v>56910</v>
+        <v>91329</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8102,35 +8107,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8138,10 +8142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317031</v>
+        <v>317047</v>
       </c>
       <c r="R58" t="n">
-        <v>6567009</v>
+        <v>6567067</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8176,17 +8180,13 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B59" t="n">
-        <v>90264</v>
+        <v>8432</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,34 +8222,36 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8257,10 +8259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R59" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8340,10 +8342,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B60" t="n">
-        <v>8432</v>
+        <v>90264</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8352,36 +8354,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R60" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335687</v>
+        <v>113336300</v>
       </c>
       <c r="B61" t="n">
-        <v>89127</v>
+        <v>89970</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317131</v>
+        <v>317034</v>
       </c>
       <c r="R61" t="n">
-        <v>6566427</v>
+        <v>6566659</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113336300</v>
+        <v>113335687</v>
       </c>
       <c r="B64" t="n">
-        <v>89970</v>
+        <v>89127</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317034</v>
+        <v>317131</v>
       </c>
       <c r="R64" t="n">
-        <v>6566659</v>
+        <v>6566427</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338164</v>
+        <v>113338079</v>
       </c>
       <c r="B65" t="n">
-        <v>55984</v>
+        <v>56765</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,41 +9004,33 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9048,10 +9040,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317128</v>
+        <v>317148</v>
       </c>
       <c r="R65" t="n">
-        <v>6566863</v>
+        <v>6566451</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9098,6 +9090,21 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9115,10 +9122,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338079</v>
+        <v>113338164</v>
       </c>
       <c r="B66" t="n">
-        <v>56765</v>
+        <v>55984</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9127,33 +9134,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9163,10 +9178,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317148</v>
+        <v>317128</v>
       </c>
       <c r="R66" t="n">
-        <v>6566451</v>
+        <v>6566863</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9213,21 +9228,6 @@
       <c r="AI66" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378087</v>
+        <v>113378352</v>
       </c>
       <c r="B68" t="n">
-        <v>90650</v>
+        <v>5163</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,30 +9391,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5454</v>
+        <v>102204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9422,10 +9424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316719</v>
+        <v>316796</v>
       </c>
       <c r="R68" t="n">
-        <v>6566788</v>
+        <v>6566783</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9477,17 +9479,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9616,10 +9618,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378364</v>
+        <v>113378087</v>
       </c>
       <c r="B70" t="n">
-        <v>94870</v>
+        <v>90650</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9632,31 +9634,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>5454</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9664,10 +9665,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316813</v>
+        <v>316719</v>
       </c>
       <c r="R70" t="n">
-        <v>6566808</v>
+        <v>6566788</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10008,10 +10009,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113377913</v>
+        <v>113378411</v>
       </c>
       <c r="B73" t="n">
-        <v>94870</v>
+        <v>4990</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10024,31 +10025,32 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10056,10 +10058,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316859</v>
+        <v>316861</v>
       </c>
       <c r="R73" t="n">
-        <v>6566682</v>
+        <v>6566893</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10121,7 +10123,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10139,7 +10141,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378035</v>
+        <v>113377913</v>
       </c>
       <c r="B74" t="n">
         <v>94870</v>
@@ -10187,10 +10189,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316688</v>
+        <v>316859</v>
       </c>
       <c r="R74" t="n">
-        <v>6566808</v>
+        <v>6566682</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10242,17 +10244,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10270,7 +10272,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113377902</v>
+        <v>113378035</v>
       </c>
       <c r="B75" t="n">
         <v>94870</v>
@@ -10318,10 +10320,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316879</v>
+        <v>316688</v>
       </c>
       <c r="R75" t="n">
-        <v>6566606</v>
+        <v>6566808</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10401,10 +10403,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378352</v>
+        <v>113378715</v>
       </c>
       <c r="B76" t="n">
-        <v>5163</v>
+        <v>90264</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10413,36 +10415,34 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102204</v>
+        <v>5260</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316796</v>
+        <v>316843</v>
       </c>
       <c r="R76" t="n">
-        <v>6566783</v>
+        <v>6567058</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10505,17 +10505,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378411</v>
+        <v>113377902</v>
       </c>
       <c r="B77" t="n">
-        <v>4990</v>
+        <v>94870</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10549,32 +10549,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>105212</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10582,10 +10581,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316861</v>
+        <v>316879</v>
       </c>
       <c r="R77" t="n">
-        <v>6566893</v>
+        <v>6566606</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10637,17 +10636,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10795,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378715</v>
+        <v>113378364</v>
       </c>
       <c r="B79" t="n">
-        <v>90264</v>
+        <v>94870</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10807,34 +10806,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316843</v>
+        <v>316813</v>
       </c>
       <c r="R79" t="n">
-        <v>6567058</v>
+        <v>6566808</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427239</v>
+        <v>113427359</v>
       </c>
       <c r="B81" t="n">
-        <v>90504</v>
+        <v>94870</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11071,30 +11071,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5467</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11102,10 +11103,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316795</v>
+        <v>316843</v>
       </c>
       <c r="R81" t="n">
-        <v>6567015</v>
+        <v>6567130</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11185,7 +11186,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113405650</v>
+        <v>113405679</v>
       </c>
       <c r="B82" t="n">
         <v>43540</v>
@@ -11234,10 +11235,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316574</v>
+        <v>316567</v>
       </c>
       <c r="R82" t="n">
-        <v>6566830</v>
+        <v>6566848</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11317,10 +11318,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113405679</v>
+        <v>113427239</v>
       </c>
       <c r="B83" t="n">
-        <v>43540</v>
+        <v>90504</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11329,36 +11330,34 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101735</v>
+        <v>5467</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11366,10 +11365,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316567</v>
+        <v>316795</v>
       </c>
       <c r="R83" t="n">
-        <v>6566848</v>
+        <v>6567015</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11396,12 +11395,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11416,22 +11415,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11579,10 +11578,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427359</v>
+        <v>113405650</v>
       </c>
       <c r="B85" t="n">
-        <v>94870</v>
+        <v>43540</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11591,35 +11590,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11627,10 +11627,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316843</v>
+        <v>316574</v>
       </c>
       <c r="R85" t="n">
-        <v>6567130</v>
+        <v>6566830</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11677,22 +11677,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B90" t="n">
-        <v>89620</v>
+        <v>90198</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R90" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,26 +12328,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12364,10 +12344,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B91" t="n">
-        <v>90198</v>
+        <v>89620</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12376,25 +12356,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12411,10 +12391,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R91" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12458,6 +12438,26 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113252817</v>
+        <v>113245476</v>
       </c>
       <c r="B43" t="n">
-        <v>89970</v>
+        <v>90516</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,28 +6165,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3242</v>
+        <v>5467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6200,10 +6196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316989</v>
+        <v>316848</v>
       </c>
       <c r="R43" t="n">
-        <v>6567074</v>
+        <v>6567253</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6265,7 +6261,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6283,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113246509</v>
+        <v>113244911</v>
       </c>
       <c r="B44" t="n">
-        <v>55984</v>
+        <v>90057</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6295,43 +6291,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6339,10 +6326,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316984</v>
+        <v>316924</v>
       </c>
       <c r="R44" t="n">
-        <v>6566956</v>
+        <v>6567085</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6383,12 +6370,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6406,10 +6409,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113244003</v>
+        <v>113244505</v>
       </c>
       <c r="B45" t="n">
-        <v>91494</v>
+        <v>89139</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6422,21 +6425,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6453,10 +6456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>316970</v>
+        <v>316987</v>
       </c>
       <c r="R45" t="n">
-        <v>6566774</v>
+        <v>6566830</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6503,7 +6506,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6518,7 +6521,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6536,10 +6539,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113245823</v>
+        <v>113243787</v>
       </c>
       <c r="B46" t="n">
-        <v>90650</v>
+        <v>90068</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6548,28 +6551,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5454</v>
+        <v>1205</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6583,10 +6590,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316794</v>
+        <v>316816</v>
       </c>
       <c r="R46" t="n">
-        <v>6567127</v>
+        <v>6566787</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6638,17 +6645,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6666,10 +6673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113245002</v>
+        <v>113246470</v>
       </c>
       <c r="B47" t="n">
-        <v>89127</v>
+        <v>56911</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6682,30 +6689,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6713,10 +6725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317012</v>
+        <v>317031</v>
       </c>
       <c r="R47" t="n">
-        <v>6566822</v>
+        <v>6567009</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6751,34 +6763,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6796,10 +6797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113243787</v>
+        <v>113244782</v>
       </c>
       <c r="B48" t="n">
-        <v>90056</v>
+        <v>89139</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6808,32 +6809,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6847,10 +6844,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316816</v>
+        <v>316904</v>
       </c>
       <c r="R48" t="n">
-        <v>6566787</v>
+        <v>6567084</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6902,17 +6899,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6930,10 +6927,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244911</v>
+        <v>113244952</v>
       </c>
       <c r="B49" t="n">
-        <v>90045</v>
+        <v>91341</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6946,24 +6943,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6977,10 +6978,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316924</v>
+        <v>317047</v>
       </c>
       <c r="R49" t="n">
-        <v>6567085</v>
+        <v>6567067</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7027,22 +7028,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Låga # Picea abies</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7060,10 +7046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113245476</v>
+        <v>113246404</v>
       </c>
       <c r="B50" t="n">
-        <v>90504</v>
+        <v>55977</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7076,30 +7062,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5467</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7107,10 +7098,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316848</v>
+        <v>316961</v>
       </c>
       <c r="R50" t="n">
-        <v>6567253</v>
+        <v>6566845</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7151,28 +7142,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7190,10 +7165,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113244725</v>
+        <v>113252817</v>
       </c>
       <c r="B51" t="n">
-        <v>90792</v>
+        <v>89982</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7202,28 +7177,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1975</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7237,10 +7216,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317004</v>
+        <v>316989</v>
       </c>
       <c r="R51" t="n">
-        <v>6566831</v>
+        <v>6567074</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7287,7 +7266,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7302,7 +7281,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7320,10 +7299,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113246470</v>
+        <v>113246434</v>
       </c>
       <c r="B52" t="n">
-        <v>56910</v>
+        <v>56766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7336,33 +7315,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7372,10 +7355,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317031</v>
+        <v>317072</v>
       </c>
       <c r="R52" t="n">
-        <v>6567009</v>
+        <v>6566964</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7410,11 +7393,6 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7427,6 +7405,21 @@
       <c r="AI52" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7444,10 +7437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113245616</v>
+        <v>113246509</v>
       </c>
       <c r="B53" t="n">
-        <v>90492</v>
+        <v>55985</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7456,34 +7449,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1213</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7491,10 +7493,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316848</v>
+        <v>316984</v>
       </c>
       <c r="R53" t="n">
-        <v>6567253</v>
+        <v>6566956</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7535,28 +7537,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7574,10 +7560,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113246434</v>
+        <v>113244003</v>
       </c>
       <c r="B54" t="n">
-        <v>56765</v>
+        <v>91506</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7590,39 +7576,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7630,10 +7607,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317072</v>
+        <v>316970</v>
       </c>
       <c r="R54" t="n">
-        <v>6566964</v>
+        <v>6566774</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7674,6 +7651,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7684,17 +7662,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7712,10 +7690,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113244505</v>
+        <v>113244725</v>
       </c>
       <c r="B55" t="n">
-        <v>89127</v>
+        <v>90804</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7724,25 +7702,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>1975</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7759,10 +7737,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316987</v>
+        <v>317004</v>
       </c>
       <c r="R55" t="n">
-        <v>6566830</v>
+        <v>6566831</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7842,10 +7820,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113246404</v>
+        <v>113245002</v>
       </c>
       <c r="B56" t="n">
-        <v>55976</v>
+        <v>89139</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7858,35 +7836,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7894,10 +7867,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316961</v>
+        <v>317012</v>
       </c>
       <c r="R56" t="n">
-        <v>6566845</v>
+        <v>6566822</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7938,12 +7911,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7961,10 +7950,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113244782</v>
+        <v>113245823</v>
       </c>
       <c r="B57" t="n">
-        <v>89127</v>
+        <v>90662</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7977,21 +7966,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>5454</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8008,10 +7997,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316904</v>
+        <v>316794</v>
       </c>
       <c r="R57" t="n">
-        <v>6567084</v>
+        <v>6567127</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8091,10 +8080,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113244952</v>
+        <v>113245616</v>
       </c>
       <c r="B58" t="n">
-        <v>91329</v>
+        <v>90504</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8107,28 +8096,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>1213</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8142,10 +8127,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317047</v>
+        <v>316848</v>
       </c>
       <c r="R58" t="n">
-        <v>6567067</v>
+        <v>6567253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8193,6 +8178,21 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8345,7 +8345,7 @@
         <v>113246376</v>
       </c>
       <c r="B60" t="n">
-        <v>90264</v>
+        <v>90276</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113336300</v>
+        <v>113335687</v>
       </c>
       <c r="B61" t="n">
-        <v>89970</v>
+        <v>89139</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317034</v>
+        <v>317131</v>
       </c>
       <c r="R61" t="n">
-        <v>6566659</v>
+        <v>6566427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113335903</v>
+        <v>113335725</v>
       </c>
       <c r="B62" t="n">
-        <v>91494</v>
+        <v>89632</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>937</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317062</v>
+        <v>317054</v>
       </c>
       <c r="R62" t="n">
-        <v>6566632</v>
+        <v>6566709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8699,22 +8699,22 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113335725</v>
+        <v>113336300</v>
       </c>
       <c r="B63" t="n">
-        <v>89620</v>
+        <v>89982</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>937</v>
+        <v>3242</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317054</v>
+        <v>317034</v>
       </c>
       <c r="R63" t="n">
-        <v>6566709</v>
+        <v>6566659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8834,17 +8834,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335687</v>
+        <v>113335903</v>
       </c>
       <c r="B64" t="n">
-        <v>89127</v>
+        <v>91506</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317131</v>
+        <v>317062</v>
       </c>
       <c r="R64" t="n">
-        <v>6566427</v>
+        <v>6566632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
         <v>113338079</v>
       </c>
       <c r="B65" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9122,10 +9122,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338164</v>
+        <v>113338739</v>
       </c>
       <c r="B66" t="n">
-        <v>55984</v>
+        <v>78133</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9134,43 +9134,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9178,10 +9169,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317128</v>
+        <v>317102</v>
       </c>
       <c r="R66" t="n">
-        <v>6566863</v>
+        <v>6566586</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9222,12 +9213,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9245,10 +9252,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B67" t="n">
-        <v>78121</v>
+        <v>55985</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9257,34 +9264,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9292,10 +9308,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R67" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9336,28 +9352,12 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378352</v>
+        <v>113378820</v>
       </c>
       <c r="B68" t="n">
-        <v>5163</v>
+        <v>94882</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,32 +9391,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102204</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9427,7 +9426,7 @@
         <v>316796</v>
       </c>
       <c r="R68" t="n">
-        <v>6566783</v>
+        <v>6567088</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9471,26 +9470,6 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Torrgren på låga # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9507,10 +9486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378820</v>
+        <v>113377902</v>
       </c>
       <c r="B69" t="n">
-        <v>94870</v>
+        <v>94882</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9555,10 +9534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316796</v>
+        <v>316879</v>
       </c>
       <c r="R69" t="n">
-        <v>6567088</v>
+        <v>6566606</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9602,6 +9581,26 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9618,10 +9617,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378087</v>
+        <v>113378352</v>
       </c>
       <c r="B70" t="n">
-        <v>90650</v>
+        <v>5163</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9634,30 +9633,32 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5454</v>
+        <v>102204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9665,10 +9666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316719</v>
+        <v>316796</v>
       </c>
       <c r="R70" t="n">
-        <v>6566788</v>
+        <v>6566783</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9720,17 +9721,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9751,7 +9752,7 @@
         <v>113377981</v>
       </c>
       <c r="B71" t="n">
-        <v>90305</v>
+        <v>90317</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9878,10 +9879,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113378774</v>
+        <v>113377913</v>
       </c>
       <c r="B72" t="n">
-        <v>94870</v>
+        <v>94882</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9926,10 +9927,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316837</v>
+        <v>316859</v>
       </c>
       <c r="R72" t="n">
-        <v>6566820</v>
+        <v>6566682</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9981,17 +9982,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10009,10 +10010,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378411</v>
+        <v>113378087</v>
       </c>
       <c r="B73" t="n">
-        <v>4990</v>
+        <v>90662</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10025,32 +10026,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105212</v>
+        <v>5454</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10058,10 +10057,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316861</v>
+        <v>316719</v>
       </c>
       <c r="R73" t="n">
-        <v>6566893</v>
+        <v>6566788</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10113,17 +10112,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10141,10 +10140,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113377913</v>
+        <v>113378172</v>
       </c>
       <c r="B74" t="n">
-        <v>94870</v>
+        <v>89632</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10157,31 +10156,30 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>937</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10189,10 +10187,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316859</v>
+        <v>316763</v>
       </c>
       <c r="R74" t="n">
-        <v>6566682</v>
+        <v>6566812</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10244,17 +10242,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10272,10 +10270,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378035</v>
+        <v>113378774</v>
       </c>
       <c r="B75" t="n">
-        <v>94870</v>
+        <v>94882</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10320,10 +10318,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316688</v>
+        <v>316837</v>
       </c>
       <c r="R75" t="n">
-        <v>6566808</v>
+        <v>6566820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10406,7 +10404,7 @@
         <v>113378715</v>
       </c>
       <c r="B76" t="n">
-        <v>90264</v>
+        <v>90276</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10533,10 +10531,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113377902</v>
+        <v>113378411</v>
       </c>
       <c r="B77" t="n">
-        <v>94870</v>
+        <v>4990</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10549,31 +10547,32 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10581,10 +10580,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316879</v>
+        <v>316861</v>
       </c>
       <c r="R77" t="n">
-        <v>6566606</v>
+        <v>6566893</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10636,17 +10635,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10664,10 +10663,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113378172</v>
+        <v>113378035</v>
       </c>
       <c r="B78" t="n">
-        <v>89620</v>
+        <v>94882</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10680,30 +10679,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316763</v>
+        <v>316688</v>
       </c>
       <c r="R78" t="n">
-        <v>6566812</v>
+        <v>6566808</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10766,17 +10766,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
         <v>113378364</v>
       </c>
       <c r="B79" t="n">
-        <v>94870</v>
+        <v>94882</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90264</v>
+        <v>90276</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427359</v>
+        <v>113427239</v>
       </c>
       <c r="B81" t="n">
-        <v>94870</v>
+        <v>90516</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11071,31 +11071,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>5467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11103,10 +11102,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316843</v>
+        <v>316795</v>
       </c>
       <c r="R81" t="n">
-        <v>6567130</v>
+        <v>6567015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11186,10 +11185,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113405679</v>
+        <v>113427359</v>
       </c>
       <c r="B82" t="n">
-        <v>43540</v>
+        <v>94882</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11198,36 +11197,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11235,10 +11233,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316567</v>
+        <v>316843</v>
       </c>
       <c r="R82" t="n">
-        <v>6566848</v>
+        <v>6567130</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11265,12 +11263,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11285,22 +11283,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11318,10 +11316,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113427239</v>
+        <v>113406315</v>
       </c>
       <c r="B83" t="n">
-        <v>90504</v>
+        <v>89982</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11334,24 +11332,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5467</v>
+        <v>3242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11365,10 +11367,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316795</v>
+        <v>316935</v>
       </c>
       <c r="R83" t="n">
-        <v>6567015</v>
+        <v>6566886</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11395,12 +11397,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11415,7 +11417,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11430,7 +11432,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11448,10 +11450,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427288</v>
+        <v>113405650</v>
       </c>
       <c r="B84" t="n">
-        <v>90264</v>
+        <v>43540</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11460,34 +11462,36 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11495,10 +11499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316863</v>
+        <v>316574</v>
       </c>
       <c r="R84" t="n">
-        <v>6567163</v>
+        <v>6566830</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11525,12 +11529,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11545,22 +11549,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11578,7 +11582,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113405650</v>
+        <v>113405679</v>
       </c>
       <c r="B85" t="n">
         <v>43540</v>
@@ -11627,10 +11631,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316574</v>
+        <v>316567</v>
       </c>
       <c r="R85" t="n">
-        <v>6566830</v>
+        <v>6566848</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11710,10 +11714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113406315</v>
+        <v>113427288</v>
       </c>
       <c r="B86" t="n">
-        <v>89970</v>
+        <v>90276</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11722,32 +11726,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3242</v>
+        <v>5260</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316935</v>
+        <v>316863</v>
       </c>
       <c r="R86" t="n">
-        <v>6566886</v>
+        <v>6567163</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11791,12 +11791,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B90" t="n">
-        <v>90198</v>
+        <v>89632</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R90" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,6 +12328,26 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12344,10 +12364,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B91" t="n">
-        <v>89620</v>
+        <v>90210</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12356,25 +12376,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12391,10 +12411,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R91" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12438,26 +12458,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90492</v>
+        <v>90504</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90447</v>
+        <v>90459</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113245476</v>
+        <v>113245002</v>
       </c>
       <c r="B43" t="n">
-        <v>90516</v>
+        <v>89139</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,21 +6165,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5467</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316848</v>
+        <v>317012</v>
       </c>
       <c r="R43" t="n">
-        <v>6567253</v>
+        <v>6566822</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6279,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113244911</v>
+        <v>113246509</v>
       </c>
       <c r="B44" t="n">
-        <v>90057</v>
+        <v>55985</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6291,34 +6291,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6326,10 +6335,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316924</v>
+        <v>316984</v>
       </c>
       <c r="R44" t="n">
-        <v>6567085</v>
+        <v>6566956</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6370,28 +6379,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Låga # Picea abies</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6409,10 +6402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113244505</v>
+        <v>113246470</v>
       </c>
       <c r="B45" t="n">
-        <v>89139</v>
+        <v>56911</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6425,30 +6418,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6456,10 +6454,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>316987</v>
+        <v>317031</v>
       </c>
       <c r="R45" t="n">
-        <v>6566830</v>
+        <v>6567009</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6494,34 +6492,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6673,10 +6660,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113246470</v>
+        <v>113245476</v>
       </c>
       <c r="B47" t="n">
-        <v>56911</v>
+        <v>90516</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6689,35 +6676,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>5467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6725,10 +6707,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317031</v>
+        <v>316848</v>
       </c>
       <c r="R47" t="n">
-        <v>6567009</v>
+        <v>6567253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6763,23 +6745,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6927,10 +6920,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244952</v>
+        <v>113244505</v>
       </c>
       <c r="B49" t="n">
-        <v>91341</v>
+        <v>89139</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6943,28 +6936,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6978,10 +6967,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>317047</v>
+        <v>316987</v>
       </c>
       <c r="R49" t="n">
-        <v>6567067</v>
+        <v>6566830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7028,7 +7017,22 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7046,10 +7050,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113246404</v>
+        <v>113245823</v>
       </c>
       <c r="B50" t="n">
-        <v>55977</v>
+        <v>90662</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7062,35 +7066,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>5454</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7098,10 +7097,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316961</v>
+        <v>316794</v>
       </c>
       <c r="R50" t="n">
-        <v>6566845</v>
+        <v>6567127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7142,12 +7141,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7165,10 +7180,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113252817</v>
+        <v>113246434</v>
       </c>
       <c r="B51" t="n">
-        <v>89982</v>
+        <v>56766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7181,21 +7196,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7203,12 +7218,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7216,10 +7236,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>316989</v>
+        <v>317072</v>
       </c>
       <c r="R51" t="n">
-        <v>6567074</v>
+        <v>6566964</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7260,7 +7280,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7271,17 +7290,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7299,10 +7318,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113246434</v>
+        <v>113245616</v>
       </c>
       <c r="B52" t="n">
-        <v>56766</v>
+        <v>90504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7315,39 +7334,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1213</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7355,10 +7365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317072</v>
+        <v>316848</v>
       </c>
       <c r="R52" t="n">
-        <v>6566964</v>
+        <v>6567253</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7399,6 +7409,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7409,17 +7420,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7437,10 +7448,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113246509</v>
+        <v>113244952</v>
       </c>
       <c r="B53" t="n">
-        <v>55985</v>
+        <v>91341</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7449,43 +7460,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7493,10 +7499,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316984</v>
+        <v>317047</v>
       </c>
       <c r="R53" t="n">
-        <v>6566956</v>
+        <v>6567067</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7537,6 +7543,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7560,10 +7567,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244003</v>
+        <v>113244725</v>
       </c>
       <c r="B54" t="n">
-        <v>91506</v>
+        <v>90804</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7572,25 +7579,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>1975</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7607,10 +7614,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316970</v>
+        <v>317004</v>
       </c>
       <c r="R54" t="n">
-        <v>6566774</v>
+        <v>6566831</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7657,7 +7664,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7672,7 +7679,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7690,10 +7697,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113244725</v>
+        <v>113244911</v>
       </c>
       <c r="B55" t="n">
-        <v>90804</v>
+        <v>90057</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7702,25 +7709,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1975</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7737,10 +7744,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317004</v>
+        <v>316924</v>
       </c>
       <c r="R55" t="n">
-        <v>6566831</v>
+        <v>6567085</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7787,22 +7794,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7820,10 +7827,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113245002</v>
+        <v>113246404</v>
       </c>
       <c r="B56" t="n">
-        <v>89139</v>
+        <v>55977</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7836,30 +7843,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7867,10 +7879,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317012</v>
+        <v>316961</v>
       </c>
       <c r="R56" t="n">
-        <v>6566822</v>
+        <v>6566845</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7911,28 +7923,12 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7950,10 +7946,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113245823</v>
+        <v>113244003</v>
       </c>
       <c r="B57" t="n">
-        <v>90662</v>
+        <v>91506</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7966,21 +7962,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5454</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7997,10 +7993,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316794</v>
+        <v>316970</v>
       </c>
       <c r="R57" t="n">
-        <v>6567127</v>
+        <v>6566774</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8062,7 +8058,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8080,10 +8076,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113245616</v>
+        <v>113252817</v>
       </c>
       <c r="B58" t="n">
-        <v>90504</v>
+        <v>89982</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8096,24 +8092,28 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1213</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>316848</v>
+        <v>316989</v>
       </c>
       <c r="R58" t="n">
-        <v>6567253</v>
+        <v>6567074</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B59" t="n">
-        <v>8432</v>
+        <v>90276</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,36 +8222,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8259,10 +8257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R59" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8342,10 +8340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B60" t="n">
-        <v>90276</v>
+        <v>8432</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8354,34 +8352,36 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R60" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335687</v>
+        <v>113336300</v>
       </c>
       <c r="B61" t="n">
-        <v>89139</v>
+        <v>89982</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317131</v>
+        <v>317034</v>
       </c>
       <c r="R61" t="n">
-        <v>6566427</v>
+        <v>6566659</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113335725</v>
+        <v>113335903</v>
       </c>
       <c r="B62" t="n">
-        <v>89632</v>
+        <v>91506</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>937</v>
+        <v>2079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317054</v>
+        <v>317062</v>
       </c>
       <c r="R62" t="n">
-        <v>6566709</v>
+        <v>6566632</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8699,22 +8699,22 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113336300</v>
+        <v>113335725</v>
       </c>
       <c r="B63" t="n">
-        <v>89982</v>
+        <v>89632</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3242</v>
+        <v>937</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317034</v>
+        <v>317054</v>
       </c>
       <c r="R63" t="n">
-        <v>6566659</v>
+        <v>6566709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8834,17 +8834,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335903</v>
+        <v>113335687</v>
       </c>
       <c r="B64" t="n">
-        <v>91506</v>
+        <v>89139</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317062</v>
+        <v>317131</v>
       </c>
       <c r="R64" t="n">
-        <v>6566632</v>
+        <v>6566427</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9122,10 +9122,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B66" t="n">
-        <v>78133</v>
+        <v>55985</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9134,34 +9134,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9169,10 +9178,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R66" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9213,28 +9222,12 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9252,10 +9245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338164</v>
+        <v>113338739</v>
       </c>
       <c r="B67" t="n">
-        <v>55985</v>
+        <v>78133</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9264,43 +9257,34 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9308,10 +9292,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317128</v>
+        <v>317102</v>
       </c>
       <c r="R67" t="n">
-        <v>6566863</v>
+        <v>6566586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9352,12 +9336,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378820</v>
+        <v>113378364</v>
       </c>
       <c r="B68" t="n">
         <v>94882</v>
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316796</v>
+        <v>316813</v>
       </c>
       <c r="R68" t="n">
-        <v>6567088</v>
+        <v>6566808</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9470,6 +9470,26 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9486,10 +9506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113377902</v>
+        <v>113378715</v>
       </c>
       <c r="B69" t="n">
-        <v>94882</v>
+        <v>90276</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9498,35 +9518,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9534,10 +9553,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316879</v>
+        <v>316843</v>
       </c>
       <c r="R69" t="n">
-        <v>6566606</v>
+        <v>6567058</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9599,7 +9618,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9617,10 +9636,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378352</v>
+        <v>113378172</v>
       </c>
       <c r="B70" t="n">
-        <v>5163</v>
+        <v>89632</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9633,32 +9652,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102204</v>
+        <v>937</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9666,10 +9683,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316796</v>
+        <v>316763</v>
       </c>
       <c r="R70" t="n">
-        <v>6566783</v>
+        <v>6566812</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9721,17 +9738,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9749,10 +9766,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113377981</v>
+        <v>113378352</v>
       </c>
       <c r="B71" t="n">
-        <v>90317</v>
+        <v>5163</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9765,30 +9782,32 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>73</v>
+        <v>102204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9796,10 +9815,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316671</v>
+        <v>316796</v>
       </c>
       <c r="R71" t="n">
-        <v>6566772</v>
+        <v>6566783</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9851,17 +9870,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10010,10 +10029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378087</v>
+        <v>113378774</v>
       </c>
       <c r="B73" t="n">
-        <v>90662</v>
+        <v>94882</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10026,30 +10045,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5454</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10057,10 +10077,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316719</v>
+        <v>316837</v>
       </c>
       <c r="R73" t="n">
-        <v>6566788</v>
+        <v>6566820</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10140,10 +10160,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378172</v>
+        <v>113378087</v>
       </c>
       <c r="B74" t="n">
-        <v>89632</v>
+        <v>90662</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10156,21 +10176,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>937</v>
+        <v>5454</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10187,10 +10207,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316763</v>
+        <v>316719</v>
       </c>
       <c r="R74" t="n">
-        <v>6566812</v>
+        <v>6566788</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10242,17 +10262,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10270,7 +10290,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378774</v>
+        <v>113377902</v>
       </c>
       <c r="B75" t="n">
         <v>94882</v>
@@ -10318,10 +10338,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316837</v>
+        <v>316879</v>
       </c>
       <c r="R75" t="n">
-        <v>6566820</v>
+        <v>6566606</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10401,10 +10421,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378715</v>
+        <v>113378035</v>
       </c>
       <c r="B76" t="n">
-        <v>90276</v>
+        <v>94882</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10413,34 +10433,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10448,10 +10469,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316843</v>
+        <v>316688</v>
       </c>
       <c r="R76" t="n">
-        <v>6567058</v>
+        <v>6566808</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10513,7 +10534,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10531,10 +10552,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378411</v>
+        <v>113378820</v>
       </c>
       <c r="B77" t="n">
-        <v>4990</v>
+        <v>94882</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10547,32 +10568,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>105212</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10580,10 +10600,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316861</v>
+        <v>316796</v>
       </c>
       <c r="R77" t="n">
-        <v>6566893</v>
+        <v>6567088</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10627,26 +10647,6 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Ståande torrträd # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10663,10 +10663,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113378035</v>
+        <v>113378411</v>
       </c>
       <c r="B78" t="n">
-        <v>94882</v>
+        <v>4990</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10679,31 +10679,32 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10711,10 +10712,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316688</v>
+        <v>316861</v>
       </c>
       <c r="R78" t="n">
-        <v>6566808</v>
+        <v>6566893</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10766,17 +10767,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10794,10 +10795,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378364</v>
+        <v>113377981</v>
       </c>
       <c r="B79" t="n">
-        <v>94882</v>
+        <v>90317</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10810,31 +10811,30 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316813</v>
+        <v>316671</v>
       </c>
       <c r="R79" t="n">
-        <v>6566808</v>
+        <v>6566772</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10897,17 +10897,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427239</v>
+        <v>113427359</v>
       </c>
       <c r="B81" t="n">
-        <v>90516</v>
+        <v>94882</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11071,30 +11071,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5467</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11102,10 +11103,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316795</v>
+        <v>316843</v>
       </c>
       <c r="R81" t="n">
-        <v>6567015</v>
+        <v>6567130</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11185,10 +11186,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113427359</v>
+        <v>113405650</v>
       </c>
       <c r="B82" t="n">
-        <v>94882</v>
+        <v>43540</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11197,35 +11198,36 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11233,10 +11235,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316843</v>
+        <v>316574</v>
       </c>
       <c r="R82" t="n">
-        <v>6567130</v>
+        <v>6566830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11263,12 +11265,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11283,22 +11285,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11450,10 +11452,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113405650</v>
+        <v>113427239</v>
       </c>
       <c r="B84" t="n">
-        <v>43540</v>
+        <v>90516</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11462,36 +11464,34 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101735</v>
+        <v>5467</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316574</v>
+        <v>316795</v>
       </c>
       <c r="R84" t="n">
-        <v>6566830</v>
+        <v>6567015</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11549,22 +11549,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113405679</v>
+        <v>113427288</v>
       </c>
       <c r="B85" t="n">
-        <v>43540</v>
+        <v>90276</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11594,36 +11594,34 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>101735</v>
+        <v>5260</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11631,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316567</v>
+        <v>316863</v>
       </c>
       <c r="R85" t="n">
-        <v>6566848</v>
+        <v>6567163</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11661,12 +11659,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11681,22 +11679,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11714,10 +11712,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113427288</v>
+        <v>113405679</v>
       </c>
       <c r="B86" t="n">
-        <v>90276</v>
+        <v>43540</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11726,34 +11724,36 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316863</v>
+        <v>316567</v>
       </c>
       <c r="R86" t="n">
-        <v>6567163</v>
+        <v>6566848</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11791,12 +11791,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11811,22 +11811,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B90" t="n">
-        <v>89632</v>
+        <v>90210</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R90" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,26 +12328,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12364,10 +12344,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B91" t="n">
-        <v>90210</v>
+        <v>89632</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12376,25 +12356,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12411,10 +12391,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R91" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12458,6 +12438,26 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6790,10 +6790,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113244782</v>
+        <v>113245823</v>
       </c>
       <c r="B48" t="n">
-        <v>89139</v>
+        <v>90662</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6806,21 +6806,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>5454</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316904</v>
+        <v>316794</v>
       </c>
       <c r="R48" t="n">
-        <v>6567084</v>
+        <v>6567127</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244505</v>
+        <v>113244782</v>
       </c>
       <c r="B49" t="n">
         <v>89139</v>
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316987</v>
+        <v>316904</v>
       </c>
       <c r="R49" t="n">
-        <v>6566830</v>
+        <v>6567084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7050,10 +7050,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113245823</v>
+        <v>113244505</v>
       </c>
       <c r="B50" t="n">
-        <v>90662</v>
+        <v>89139</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5454</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7097,10 +7097,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316794</v>
+        <v>316987</v>
       </c>
       <c r="R50" t="n">
-        <v>6567127</v>
+        <v>6566830</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113244952</v>
+        <v>113244725</v>
       </c>
       <c r="B53" t="n">
-        <v>91341</v>
+        <v>90804</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7460,32 +7460,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1975</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kauffman) Jülich</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7499,10 +7495,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317047</v>
+        <v>317004</v>
       </c>
       <c r="R53" t="n">
-        <v>6567067</v>
+        <v>6566831</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7549,7 +7545,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7567,10 +7578,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244725</v>
+        <v>113244952</v>
       </c>
       <c r="B54" t="n">
-        <v>90804</v>
+        <v>91341</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7579,28 +7590,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1975</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7614,10 +7629,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317004</v>
+        <v>317047</v>
       </c>
       <c r="R54" t="n">
-        <v>6566831</v>
+        <v>6567067</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7664,22 +7679,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113245002</v>
+        <v>113244782</v>
       </c>
       <c r="B43" t="n">
-        <v>89139</v>
+        <v>89161</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317012</v>
+        <v>316904</v>
       </c>
       <c r="R43" t="n">
-        <v>6566822</v>
+        <v>6567084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6279,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113246509</v>
+        <v>113244003</v>
       </c>
       <c r="B44" t="n">
-        <v>55985</v>
+        <v>91528</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6291,43 +6291,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6335,10 +6326,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316984</v>
+        <v>316970</v>
       </c>
       <c r="R44" t="n">
-        <v>6566956</v>
+        <v>6566774</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6379,12 +6370,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6402,10 +6409,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113246470</v>
+        <v>113245002</v>
       </c>
       <c r="B45" t="n">
-        <v>56911</v>
+        <v>89161</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6418,35 +6425,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6454,10 +6456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317031</v>
+        <v>317012</v>
       </c>
       <c r="R45" t="n">
-        <v>6567009</v>
+        <v>6566822</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6492,23 +6494,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6526,10 +6539,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113243787</v>
+        <v>113245823</v>
       </c>
       <c r="B46" t="n">
-        <v>90068</v>
+        <v>90684</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6538,32 +6551,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1205</v>
+        <v>5454</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6577,10 +6586,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316816</v>
+        <v>316794</v>
       </c>
       <c r="R46" t="n">
-        <v>6566787</v>
+        <v>6567127</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6632,17 +6641,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6660,10 +6669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113245476</v>
+        <v>113244725</v>
       </c>
       <c r="B47" t="n">
-        <v>90516</v>
+        <v>90826</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6672,25 +6681,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5467</v>
+        <v>1975</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6707,10 +6716,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316848</v>
+        <v>317004</v>
       </c>
       <c r="R47" t="n">
-        <v>6567253</v>
+        <v>6566831</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6757,7 +6766,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6790,10 +6799,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113245823</v>
+        <v>113244505</v>
       </c>
       <c r="B48" t="n">
-        <v>90662</v>
+        <v>89161</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6806,21 +6815,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5454</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6837,10 +6846,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316794</v>
+        <v>316987</v>
       </c>
       <c r="R48" t="n">
-        <v>6567127</v>
+        <v>6566830</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6887,7 +6896,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6920,10 +6929,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244782</v>
+        <v>113245616</v>
       </c>
       <c r="B49" t="n">
-        <v>89139</v>
+        <v>90526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6936,21 +6945,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>1213</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6967,10 +6976,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316904</v>
+        <v>316848</v>
       </c>
       <c r="R49" t="n">
-        <v>6567084</v>
+        <v>6567253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7050,10 +7059,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113244505</v>
+        <v>113245442</v>
       </c>
       <c r="B50" t="n">
-        <v>89139</v>
+        <v>90538</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7066,21 +7075,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>5467</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7097,10 +7106,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316987</v>
+        <v>316848</v>
       </c>
       <c r="R50" t="n">
-        <v>6566830</v>
+        <v>6567253</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7147,7 +7156,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7180,10 +7189,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113246434</v>
+        <v>113246470</v>
       </c>
       <c r="B51" t="n">
-        <v>56766</v>
+        <v>56911</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7196,37 +7205,33 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7236,10 +7241,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317072</v>
+        <v>317031</v>
       </c>
       <c r="R51" t="n">
-        <v>6566964</v>
+        <v>6567009</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7274,6 +7279,11 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7286,21 +7296,6 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7318,10 +7313,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113245616</v>
+        <v>113246434</v>
       </c>
       <c r="B52" t="n">
-        <v>90504</v>
+        <v>56766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7334,30 +7329,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1213</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7365,10 +7369,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316848</v>
+        <v>317072</v>
       </c>
       <c r="R52" t="n">
-        <v>6567253</v>
+        <v>6566964</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7409,7 +7413,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7420,17 +7423,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7448,10 +7451,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113244725</v>
+        <v>113244952</v>
       </c>
       <c r="B53" t="n">
-        <v>90804</v>
+        <v>91363</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7460,28 +7463,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1975</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7495,10 +7502,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317004</v>
+        <v>317047</v>
       </c>
       <c r="R53" t="n">
-        <v>6566831</v>
+        <v>6567067</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7545,22 +7552,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7578,10 +7570,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244952</v>
+        <v>113246509</v>
       </c>
       <c r="B54" t="n">
-        <v>91341</v>
+        <v>55985</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7590,38 +7582,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7629,10 +7626,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317047</v>
+        <v>316984</v>
       </c>
       <c r="R54" t="n">
-        <v>6567067</v>
+        <v>6566956</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7673,7 +7670,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7697,10 +7693,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113244911</v>
+        <v>113252817</v>
       </c>
       <c r="B55" t="n">
-        <v>90057</v>
+        <v>90004</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7713,24 +7709,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>3242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316924</v>
+        <v>316989</v>
       </c>
       <c r="R55" t="n">
-        <v>6567085</v>
+        <v>6567074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7794,22 +7794,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113244003</v>
+        <v>113244911</v>
       </c>
       <c r="B57" t="n">
-        <v>91506</v>
+        <v>90079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7962,21 +7962,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316970</v>
+        <v>316924</v>
       </c>
       <c r="R57" t="n">
-        <v>6566774</v>
+        <v>6567085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8043,22 +8043,22 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113252817</v>
+        <v>113243787</v>
       </c>
       <c r="B58" t="n">
-        <v>89982</v>
+        <v>90090</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8088,25 +8088,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>316989</v>
+        <v>316816</v>
       </c>
       <c r="R58" t="n">
-        <v>6567074</v>
+        <v>6566787</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8182,17 +8182,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
         <v>113246376</v>
       </c>
       <c r="B59" t="n">
-        <v>90276</v>
+        <v>90298</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113336300</v>
+        <v>113335687</v>
       </c>
       <c r="B61" t="n">
-        <v>89982</v>
+        <v>89161</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317034</v>
+        <v>317131</v>
       </c>
       <c r="R61" t="n">
-        <v>6566659</v>
+        <v>6566427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
         <v>113335903</v>
       </c>
       <c r="B62" t="n">
-        <v>91506</v>
+        <v>91528</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>113335725</v>
       </c>
       <c r="B63" t="n">
-        <v>89632</v>
+        <v>89654</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335687</v>
+        <v>113336300</v>
       </c>
       <c r="B64" t="n">
-        <v>89139</v>
+        <v>90004</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317131</v>
+        <v>317034</v>
       </c>
       <c r="R64" t="n">
-        <v>6566427</v>
+        <v>6566659</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338079</v>
+        <v>113338164</v>
       </c>
       <c r="B65" t="n">
-        <v>56766</v>
+        <v>55985</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,33 +9004,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9040,10 +9048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317148</v>
+        <v>317128</v>
       </c>
       <c r="R65" t="n">
-        <v>6566451</v>
+        <v>6566863</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9090,21 +9098,6 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9122,10 +9115,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338164</v>
+        <v>113338079</v>
       </c>
       <c r="B66" t="n">
-        <v>55985</v>
+        <v>56766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9134,41 +9127,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9178,10 +9163,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317128</v>
+        <v>317148</v>
       </c>
       <c r="R66" t="n">
-        <v>6566863</v>
+        <v>6566451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9228,6 +9213,21 @@
       <c r="AI66" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
         <v>113338739</v>
       </c>
       <c r="B67" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378364</v>
+        <v>113378035</v>
       </c>
       <c r="B68" t="n">
-        <v>94882</v>
+        <v>94904</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316813</v>
+        <v>316688</v>
       </c>
       <c r="R68" t="n">
         <v>6566808</v>
@@ -9506,10 +9506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378715</v>
+        <v>113378352</v>
       </c>
       <c r="B69" t="n">
-        <v>90276</v>
+        <v>5163</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9518,34 +9518,36 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5260</v>
+        <v>102204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9553,10 +9555,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316843</v>
+        <v>316796</v>
       </c>
       <c r="R69" t="n">
-        <v>6567058</v>
+        <v>6566783</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9608,17 +9610,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9636,10 +9638,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378172</v>
+        <v>113378087</v>
       </c>
       <c r="B70" t="n">
-        <v>89632</v>
+        <v>90684</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9652,21 +9654,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>937</v>
+        <v>5454</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9683,10 +9685,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316763</v>
+        <v>316719</v>
       </c>
       <c r="R70" t="n">
-        <v>6566812</v>
+        <v>6566788</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9738,17 +9740,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9766,10 +9768,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378352</v>
+        <v>113378364</v>
       </c>
       <c r="B71" t="n">
-        <v>5163</v>
+        <v>94904</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9782,32 +9784,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102204</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9815,10 +9816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316796</v>
+        <v>316813</v>
       </c>
       <c r="R71" t="n">
-        <v>6566783</v>
+        <v>6566808</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9870,17 +9871,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9898,10 +9899,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113377913</v>
+        <v>113377981</v>
       </c>
       <c r="B72" t="n">
-        <v>94882</v>
+        <v>90339</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9914,31 +9915,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316859</v>
+        <v>316671</v>
       </c>
       <c r="R72" t="n">
-        <v>6566682</v>
+        <v>6566772</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10001,17 +10001,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10029,10 +10029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378774</v>
+        <v>113378411</v>
       </c>
       <c r="B73" t="n">
-        <v>94882</v>
+        <v>4990</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10045,31 +10045,32 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10077,10 +10078,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316837</v>
+        <v>316861</v>
       </c>
       <c r="R73" t="n">
-        <v>6566820</v>
+        <v>6566893</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10132,17 +10133,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10160,10 +10161,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378087</v>
+        <v>113378172</v>
       </c>
       <c r="B74" t="n">
-        <v>90662</v>
+        <v>89654</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10176,21 +10177,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5454</v>
+        <v>937</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10207,10 +10208,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316719</v>
+        <v>316763</v>
       </c>
       <c r="R74" t="n">
-        <v>6566788</v>
+        <v>6566812</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10262,17 +10263,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10290,10 +10291,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113377902</v>
+        <v>113378820</v>
       </c>
       <c r="B75" t="n">
-        <v>94882</v>
+        <v>94904</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10338,10 +10339,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316879</v>
+        <v>316796</v>
       </c>
       <c r="R75" t="n">
-        <v>6566606</v>
+        <v>6567088</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10385,26 +10386,6 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10421,10 +10402,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378035</v>
+        <v>113377913</v>
       </c>
       <c r="B76" t="n">
-        <v>94882</v>
+        <v>94904</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10469,10 +10450,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316688</v>
+        <v>316859</v>
       </c>
       <c r="R76" t="n">
-        <v>6566808</v>
+        <v>6566682</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10524,17 +10505,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10552,10 +10533,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378820</v>
+        <v>113377902</v>
       </c>
       <c r="B77" t="n">
-        <v>94882</v>
+        <v>94904</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10600,10 +10581,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316796</v>
+        <v>316879</v>
       </c>
       <c r="R77" t="n">
-        <v>6567088</v>
+        <v>6566606</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10647,6 +10628,26 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10663,10 +10664,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113378411</v>
+        <v>113378715</v>
       </c>
       <c r="B78" t="n">
-        <v>4990</v>
+        <v>90298</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10675,36 +10676,34 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105212</v>
+        <v>5260</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10712,10 +10711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316861</v>
+        <v>316843</v>
       </c>
       <c r="R78" t="n">
-        <v>6566893</v>
+        <v>6567058</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10767,17 +10766,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10795,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113377981</v>
+        <v>113378774</v>
       </c>
       <c r="B79" t="n">
-        <v>90317</v>
+        <v>94904</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10811,30 +10810,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316671</v>
+        <v>316837</v>
       </c>
       <c r="R79" t="n">
-        <v>6566772</v>
+        <v>6566820</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10897,17 +10897,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90276</v>
+        <v>90298</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>113427359</v>
       </c>
       <c r="B81" t="n">
-        <v>94882</v>
+        <v>94904</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113405650</v>
+        <v>113427288</v>
       </c>
       <c r="B82" t="n">
-        <v>43540</v>
+        <v>90298</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11198,36 +11198,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>5260</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11235,10 +11233,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316574</v>
+        <v>316863</v>
       </c>
       <c r="R82" t="n">
-        <v>6566830</v>
+        <v>6567163</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11265,12 +11263,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11285,22 +11283,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11318,10 +11316,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113406315</v>
+        <v>113427239</v>
       </c>
       <c r="B83" t="n">
-        <v>89982</v>
+        <v>90538</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11334,28 +11332,24 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3242</v>
+        <v>5467</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11369,10 +11363,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316935</v>
+        <v>316795</v>
       </c>
       <c r="R83" t="n">
-        <v>6566886</v>
+        <v>6567015</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11399,12 +11393,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11419,7 +11413,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11434,7 +11428,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11452,10 +11446,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427239</v>
+        <v>113406315</v>
       </c>
       <c r="B84" t="n">
-        <v>90516</v>
+        <v>90004</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11468,24 +11462,28 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5467</v>
+        <v>3242</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11499,10 +11497,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316795</v>
+        <v>316935</v>
       </c>
       <c r="R84" t="n">
-        <v>6567015</v>
+        <v>6566886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11529,12 +11527,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11549,7 +11547,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11564,7 +11562,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11582,10 +11580,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427288</v>
+        <v>113405679</v>
       </c>
       <c r="B85" t="n">
-        <v>90276</v>
+        <v>43540</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11594,34 +11592,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316863</v>
+        <v>316567</v>
       </c>
       <c r="R85" t="n">
-        <v>6567163</v>
+        <v>6566848</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11679,22 +11679,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11712,7 +11712,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113405679</v>
+        <v>113405650</v>
       </c>
       <c r="B86" t="n">
         <v>43540</v>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316567</v>
+        <v>316574</v>
       </c>
       <c r="R86" t="n">
-        <v>6566848</v>
+        <v>6566830</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -12237,7 +12237,7 @@
         <v>113245275</v>
       </c>
       <c r="B90" t="n">
-        <v>90210</v>
+        <v>90232</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>113245353</v>
       </c>
       <c r="B91" t="n">
-        <v>89632</v>
+        <v>89654</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90504</v>
+        <v>90526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90459</v>
+        <v>90481</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -7059,10 +7059,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113245442</v>
+        <v>113246470</v>
       </c>
       <c r="B50" t="n">
-        <v>90538</v>
+        <v>56911</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7075,30 +7075,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5467</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7106,10 +7111,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316848</v>
+        <v>317031</v>
       </c>
       <c r="R50" t="n">
-        <v>6567253</v>
+        <v>6567009</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7144,34 +7149,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7189,10 +7183,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113246470</v>
+        <v>113246434</v>
       </c>
       <c r="B51" t="n">
-        <v>56911</v>
+        <v>56766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7205,33 +7199,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7241,10 +7239,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317031</v>
+        <v>317072</v>
       </c>
       <c r="R51" t="n">
-        <v>6567009</v>
+        <v>6566964</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7279,11 +7277,6 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7296,6 +7289,21 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7313,10 +7321,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113246434</v>
+        <v>113245442</v>
       </c>
       <c r="B52" t="n">
-        <v>56766</v>
+        <v>90538</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7329,39 +7337,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7369,10 +7368,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317072</v>
+        <v>316848</v>
       </c>
       <c r="R52" t="n">
-        <v>6566964</v>
+        <v>6567253</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7413,6 +7412,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7423,17 +7423,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113244782</v>
+        <v>113246434</v>
       </c>
       <c r="B43" t="n">
-        <v>89161</v>
+        <v>56769</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,30 +6165,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6196,10 +6205,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316904</v>
+        <v>317072</v>
       </c>
       <c r="R43" t="n">
-        <v>6567084</v>
+        <v>6566964</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6240,7 +6249,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6251,17 +6259,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6279,10 +6287,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113244003</v>
+        <v>113245002</v>
       </c>
       <c r="B44" t="n">
-        <v>91528</v>
+        <v>89165</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6295,21 +6303,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6326,10 +6334,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316970</v>
+        <v>317012</v>
       </c>
       <c r="R44" t="n">
-        <v>6566774</v>
+        <v>6566822</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6376,7 +6384,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6391,7 +6399,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6409,10 +6417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113245002</v>
+        <v>113246509</v>
       </c>
       <c r="B45" t="n">
-        <v>89161</v>
+        <v>55988</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6421,34 +6429,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6456,10 +6473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317012</v>
+        <v>316984</v>
       </c>
       <c r="R45" t="n">
-        <v>6566822</v>
+        <v>6566956</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6500,28 +6517,12 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6539,10 +6540,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113245823</v>
+        <v>113243787</v>
       </c>
       <c r="B46" t="n">
-        <v>90684</v>
+        <v>90094</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6551,28 +6552,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5454</v>
+        <v>1205</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6586,10 +6591,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316794</v>
+        <v>316816</v>
       </c>
       <c r="R46" t="n">
-        <v>6567127</v>
+        <v>6566787</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6641,17 +6646,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6672,7 +6677,7 @@
         <v>113244725</v>
       </c>
       <c r="B47" t="n">
-        <v>90826</v>
+        <v>90830</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6799,10 +6804,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113244505</v>
+        <v>113245476</v>
       </c>
       <c r="B48" t="n">
-        <v>89161</v>
+        <v>90542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6815,21 +6820,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>5467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6846,10 +6851,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316987</v>
+        <v>316848</v>
       </c>
       <c r="R48" t="n">
-        <v>6566830</v>
+        <v>6567253</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6896,7 +6901,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6929,10 +6934,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113245616</v>
+        <v>113244782</v>
       </c>
       <c r="B49" t="n">
-        <v>90526</v>
+        <v>89165</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6945,21 +6950,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1213</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6976,10 +6981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316848</v>
+        <v>316904</v>
       </c>
       <c r="R49" t="n">
-        <v>6567253</v>
+        <v>6567084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7059,10 +7064,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113246470</v>
+        <v>113245823</v>
       </c>
       <c r="B50" t="n">
-        <v>56911</v>
+        <v>90688</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7075,35 +7080,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>5454</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>317031</v>
+        <v>316794</v>
       </c>
       <c r="R50" t="n">
-        <v>6567009</v>
+        <v>6567127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7149,23 +7149,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7183,10 +7194,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113246434</v>
+        <v>113244003</v>
       </c>
       <c r="B51" t="n">
-        <v>56766</v>
+        <v>91532</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7199,39 +7210,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7239,10 +7241,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317072</v>
+        <v>316970</v>
       </c>
       <c r="R51" t="n">
-        <v>6566964</v>
+        <v>6566774</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7283,6 +7285,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7293,17 +7296,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7321,10 +7324,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113245442</v>
+        <v>113252817</v>
       </c>
       <c r="B52" t="n">
-        <v>90538</v>
+        <v>90008</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7337,24 +7340,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>3242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7368,10 +7375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316848</v>
+        <v>316989</v>
       </c>
       <c r="R52" t="n">
-        <v>6567253</v>
+        <v>6567074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7433,7 +7440,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7451,10 +7458,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113244952</v>
+        <v>113246404</v>
       </c>
       <c r="B53" t="n">
-        <v>91363</v>
+        <v>55980</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7467,21 +7474,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -7489,12 +7496,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7502,10 +7510,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317047</v>
+        <v>316961</v>
       </c>
       <c r="R53" t="n">
-        <v>6567067</v>
+        <v>6566845</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7546,13 +7554,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7570,10 +7577,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113246509</v>
+        <v>113244505</v>
       </c>
       <c r="B54" t="n">
-        <v>55985</v>
+        <v>89165</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7582,43 +7589,34 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7626,10 +7624,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316984</v>
+        <v>316987</v>
       </c>
       <c r="R54" t="n">
-        <v>6566956</v>
+        <v>6566830</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7670,12 +7668,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7693,10 +7707,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113252817</v>
+        <v>113246470</v>
       </c>
       <c r="B55" t="n">
-        <v>90004</v>
+        <v>56914</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7709,34 +7723,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3242</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7744,10 +7759,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316989</v>
+        <v>317031</v>
       </c>
       <c r="R55" t="n">
-        <v>6567074</v>
+        <v>6567009</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7782,34 +7797,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7827,10 +7831,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113246404</v>
+        <v>113244911</v>
       </c>
       <c r="B56" t="n">
-        <v>55977</v>
+        <v>90083</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7843,35 +7847,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7879,10 +7878,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316961</v>
+        <v>316924</v>
       </c>
       <c r="R56" t="n">
-        <v>6566845</v>
+        <v>6567085</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7923,12 +7922,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7946,10 +7961,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113244911</v>
+        <v>113245616</v>
       </c>
       <c r="B57" t="n">
-        <v>90079</v>
+        <v>90530</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7962,21 +7977,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>1213</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7993,10 +8008,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316924</v>
+        <v>316848</v>
       </c>
       <c r="R57" t="n">
-        <v>6567085</v>
+        <v>6567253</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8043,22 +8058,22 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8076,10 +8091,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113243787</v>
+        <v>113244952</v>
       </c>
       <c r="B58" t="n">
-        <v>90090</v>
+        <v>91367</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8088,25 +8103,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8127,10 +8142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>316816</v>
+        <v>317047</v>
       </c>
       <c r="R58" t="n">
-        <v>6566787</v>
+        <v>6567067</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8178,21 +8193,6 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B59" t="n">
-        <v>90298</v>
+        <v>8432</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,34 +8222,36 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8257,10 +8259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R59" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8340,10 +8342,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B60" t="n">
-        <v>8432</v>
+        <v>90302</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8352,36 +8354,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R60" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335687</v>
+        <v>113335725</v>
       </c>
       <c r="B61" t="n">
-        <v>89161</v>
+        <v>89658</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>937</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317131</v>
+        <v>317054</v>
       </c>
       <c r="R61" t="n">
-        <v>6566427</v>
+        <v>6566709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,22 +8569,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
         <v>113335903</v>
       </c>
       <c r="B62" t="n">
-        <v>91528</v>
+        <v>91532</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113335725</v>
+        <v>113336300</v>
       </c>
       <c r="B63" t="n">
-        <v>89654</v>
+        <v>90008</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>937</v>
+        <v>3242</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317054</v>
+        <v>317034</v>
       </c>
       <c r="R63" t="n">
-        <v>6566709</v>
+        <v>6566659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8834,17 +8834,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113336300</v>
+        <v>113335687</v>
       </c>
       <c r="B64" t="n">
-        <v>90004</v>
+        <v>89165</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317034</v>
+        <v>317131</v>
       </c>
       <c r="R64" t="n">
-        <v>6566659</v>
+        <v>6566427</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338164</v>
+        <v>113338739</v>
       </c>
       <c r="B65" t="n">
-        <v>55985</v>
+        <v>78158</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,43 +9004,34 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9048,10 +9039,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317128</v>
+        <v>317102</v>
       </c>
       <c r="R65" t="n">
-        <v>6566863</v>
+        <v>6566586</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9092,12 +9083,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9118,7 +9125,7 @@
         <v>113338079</v>
       </c>
       <c r="B66" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9245,10 +9252,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B67" t="n">
-        <v>78155</v>
+        <v>55988</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9257,34 +9264,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9292,10 +9308,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R67" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9336,28 +9352,12 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378035</v>
+        <v>113378352</v>
       </c>
       <c r="B68" t="n">
-        <v>94904</v>
+        <v>5163</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,31 +9391,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9423,10 +9424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316688</v>
+        <v>316796</v>
       </c>
       <c r="R68" t="n">
-        <v>6566808</v>
+        <v>6566783</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9478,17 +9479,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9506,10 +9507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378352</v>
+        <v>113378820</v>
       </c>
       <c r="B69" t="n">
-        <v>5163</v>
+        <v>94908</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9522,32 +9523,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102204</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>316796</v>
       </c>
       <c r="R69" t="n">
-        <v>6566783</v>
+        <v>6567088</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9602,26 +9602,6 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Torrgren på låga # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9638,10 +9618,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378087</v>
+        <v>113378411</v>
       </c>
       <c r="B70" t="n">
-        <v>90684</v>
+        <v>4990</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9654,30 +9634,32 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5454</v>
+        <v>105212</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9685,10 +9667,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316719</v>
+        <v>316861</v>
       </c>
       <c r="R70" t="n">
-        <v>6566788</v>
+        <v>6566893</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9740,17 +9722,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9768,10 +9750,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378364</v>
+        <v>113378172</v>
       </c>
       <c r="B71" t="n">
-        <v>94904</v>
+        <v>89658</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9784,31 +9766,30 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>937</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9816,10 +9797,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316813</v>
+        <v>316763</v>
       </c>
       <c r="R71" t="n">
-        <v>6566808</v>
+        <v>6566812</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9871,17 +9852,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9902,7 +9883,7 @@
         <v>113377981</v>
       </c>
       <c r="B72" t="n">
-        <v>90339</v>
+        <v>90343</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10029,10 +10010,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378411</v>
+        <v>113377913</v>
       </c>
       <c r="B73" t="n">
-        <v>4990</v>
+        <v>94908</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10045,32 +10026,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105212</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10078,10 +10058,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316861</v>
+        <v>316859</v>
       </c>
       <c r="R73" t="n">
-        <v>6566893</v>
+        <v>6566682</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10143,7 +10123,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10161,10 +10141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378172</v>
+        <v>113378715</v>
       </c>
       <c r="B74" t="n">
-        <v>89654</v>
+        <v>90302</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10173,25 +10153,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>937</v>
+        <v>5260</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10208,10 +10188,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316763</v>
+        <v>316843</v>
       </c>
       <c r="R74" t="n">
-        <v>6566812</v>
+        <v>6567058</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10263,17 +10243,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10291,10 +10271,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378820</v>
+        <v>113378774</v>
       </c>
       <c r="B75" t="n">
-        <v>94904</v>
+        <v>94908</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10339,10 +10319,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316796</v>
+        <v>316837</v>
       </c>
       <c r="R75" t="n">
-        <v>6567088</v>
+        <v>6566820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10386,6 +10366,26 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113377913</v>
+        <v>113378087</v>
       </c>
       <c r="B76" t="n">
-        <v>94904</v>
+        <v>90688</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10418,31 +10418,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>5454</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10450,10 +10449,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316859</v>
+        <v>316719</v>
       </c>
       <c r="R76" t="n">
-        <v>6566682</v>
+        <v>6566788</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10505,17 +10504,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10533,10 +10532,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113377902</v>
+        <v>113378035</v>
       </c>
       <c r="B77" t="n">
-        <v>94904</v>
+        <v>94908</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10581,10 +10580,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316879</v>
+        <v>316688</v>
       </c>
       <c r="R77" t="n">
-        <v>6566606</v>
+        <v>6566808</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10664,10 +10663,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113378715</v>
+        <v>113377902</v>
       </c>
       <c r="B78" t="n">
-        <v>90298</v>
+        <v>94908</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10676,34 +10675,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316843</v>
+        <v>316879</v>
       </c>
       <c r="R78" t="n">
-        <v>6567058</v>
+        <v>6566606</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10794,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378774</v>
+        <v>113378364</v>
       </c>
       <c r="B79" t="n">
-        <v>94904</v>
+        <v>94908</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316837</v>
+        <v>316813</v>
       </c>
       <c r="R79" t="n">
-        <v>6566820</v>
+        <v>6566808</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90298</v>
+        <v>90302</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427359</v>
+        <v>113405679</v>
       </c>
       <c r="B81" t="n">
-        <v>94904</v>
+        <v>43542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11067,35 +11067,36 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11103,10 +11104,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316843</v>
+        <v>316567</v>
       </c>
       <c r="R81" t="n">
-        <v>6567130</v>
+        <v>6566848</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11133,12 +11134,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11153,22 +11154,22 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11189,7 +11190,7 @@
         <v>113427288</v>
       </c>
       <c r="B82" t="n">
-        <v>90298</v>
+        <v>90302</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11319,7 +11320,7 @@
         <v>113427239</v>
       </c>
       <c r="B83" t="n">
-        <v>90538</v>
+        <v>90542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11446,10 +11447,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113406315</v>
+        <v>113427359</v>
       </c>
       <c r="B84" t="n">
-        <v>90004</v>
+        <v>94908</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11462,34 +11463,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3242</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11497,10 +11495,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316935</v>
+        <v>316843</v>
       </c>
       <c r="R84" t="n">
-        <v>6566886</v>
+        <v>6567130</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11527,12 +11525,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11547,7 +11545,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11562,7 +11560,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11580,10 +11578,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113405679</v>
+        <v>113406315</v>
       </c>
       <c r="B85" t="n">
-        <v>43540</v>
+        <v>90008</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11592,36 +11590,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316567</v>
+        <v>316935</v>
       </c>
       <c r="R85" t="n">
-        <v>6566848</v>
+        <v>6566886</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11679,22 +11679,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
         <v>113405650</v>
       </c>
       <c r="B86" t="n">
-        <v>43540</v>
+        <v>43542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B90" t="n">
-        <v>90232</v>
+        <v>89658</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R90" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,6 +12328,26 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12344,10 +12364,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B91" t="n">
-        <v>89654</v>
+        <v>90236</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12356,25 +12376,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12391,10 +12411,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R91" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12438,26 +12458,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90526</v>
+        <v>90530</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90481</v>
+        <v>90485</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6804,7 +6804,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113245476</v>
+        <v>113245442</v>
       </c>
       <c r="B48" t="n">
         <v>90542</v>
@@ -7324,10 +7324,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113252817</v>
+        <v>113246404</v>
       </c>
       <c r="B52" t="n">
-        <v>90008</v>
+        <v>55980</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3242</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7362,12 +7362,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7375,10 +7376,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316989</v>
+        <v>316961</v>
       </c>
       <c r="R52" t="n">
-        <v>6567074</v>
+        <v>6566845</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7419,28 +7420,12 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7458,10 +7443,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113246404</v>
+        <v>113252817</v>
       </c>
       <c r="B53" t="n">
-        <v>55980</v>
+        <v>90008</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7474,21 +7459,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -7496,13 +7481,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7510,10 +7494,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316961</v>
+        <v>316989</v>
       </c>
       <c r="R53" t="n">
-        <v>6566845</v>
+        <v>6567074</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7554,12 +7538,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244505</v>
+        <v>113246470</v>
       </c>
       <c r="B54" t="n">
-        <v>89165</v>
+        <v>56914</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7593,30 +7593,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7624,10 +7629,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316987</v>
+        <v>317031</v>
       </c>
       <c r="R54" t="n">
-        <v>6566830</v>
+        <v>6567009</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7662,34 +7667,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7707,10 +7701,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113246470</v>
+        <v>113244505</v>
       </c>
       <c r="B55" t="n">
-        <v>56914</v>
+        <v>89165</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7723,35 +7717,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7759,10 +7748,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317031</v>
+        <v>316987</v>
       </c>
       <c r="R55" t="n">
-        <v>6567009</v>
+        <v>6566830</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7797,23 +7786,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113246434</v>
+        <v>113245442</v>
       </c>
       <c r="B43" t="n">
-        <v>56769</v>
+        <v>90542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6165,39 +6165,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6205,10 +6196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317072</v>
+        <v>316848</v>
       </c>
       <c r="R43" t="n">
-        <v>6566964</v>
+        <v>6567253</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6249,6 +6240,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6259,17 +6251,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6287,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113245002</v>
+        <v>113245616</v>
       </c>
       <c r="B44" t="n">
-        <v>89165</v>
+        <v>90530</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6303,21 +6295,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>1213</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6334,10 +6326,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317012</v>
+        <v>316848</v>
       </c>
       <c r="R44" t="n">
-        <v>6566822</v>
+        <v>6567253</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6384,7 +6376,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6417,10 +6409,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113246509</v>
+        <v>113245002</v>
       </c>
       <c r="B45" t="n">
-        <v>55988</v>
+        <v>89165</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6429,43 +6421,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6473,10 +6456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>316984</v>
+        <v>317012</v>
       </c>
       <c r="R45" t="n">
-        <v>6566956</v>
+        <v>6566822</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6517,12 +6500,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6540,10 +6539,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113243787</v>
+        <v>113244505</v>
       </c>
       <c r="B46" t="n">
-        <v>90094</v>
+        <v>89165</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6552,32 +6551,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1205</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6591,10 +6586,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316816</v>
+        <v>316987</v>
       </c>
       <c r="R46" t="n">
-        <v>6566787</v>
+        <v>6566830</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6641,22 +6636,22 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6674,10 +6669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113244725</v>
+        <v>113244003</v>
       </c>
       <c r="B47" t="n">
-        <v>90830</v>
+        <v>91532</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6686,25 +6681,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1975</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6721,10 +6716,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317004</v>
+        <v>316970</v>
       </c>
       <c r="R47" t="n">
-        <v>6566831</v>
+        <v>6566774</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6771,7 +6766,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6786,7 +6781,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6804,10 +6799,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113245442</v>
+        <v>113243787</v>
       </c>
       <c r="B48" t="n">
-        <v>90542</v>
+        <v>90094</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6816,28 +6811,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5467</v>
+        <v>1205</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6851,10 +6850,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316848</v>
+        <v>316816</v>
       </c>
       <c r="R48" t="n">
-        <v>6567253</v>
+        <v>6566787</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6906,17 +6905,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7194,10 +7193,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113244003</v>
+        <v>113244952</v>
       </c>
       <c r="B51" t="n">
-        <v>91532</v>
+        <v>91367</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7210,24 +7209,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2079</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7241,10 +7244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>316970</v>
+        <v>317047</v>
       </c>
       <c r="R51" t="n">
-        <v>6566774</v>
+        <v>6567067</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7292,21 +7295,6 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7324,10 +7312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113246404</v>
+        <v>113246470</v>
       </c>
       <c r="B52" t="n">
-        <v>55980</v>
+        <v>56914</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7340,35 +7328,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7376,10 +7364,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316961</v>
+        <v>317031</v>
       </c>
       <c r="R52" t="n">
-        <v>6566845</v>
+        <v>6567009</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7414,6 +7402,11 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7425,7 +7418,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7443,10 +7436,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113252817</v>
+        <v>113244725</v>
       </c>
       <c r="B53" t="n">
-        <v>90008</v>
+        <v>90830</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7455,32 +7448,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>1975</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kauffman) Jülich</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7494,10 +7483,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316989</v>
+        <v>317004</v>
       </c>
       <c r="R53" t="n">
-        <v>6567074</v>
+        <v>6566831</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7544,7 +7533,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7559,7 +7548,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7577,10 +7566,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113246470</v>
+        <v>113246404</v>
       </c>
       <c r="B54" t="n">
-        <v>56914</v>
+        <v>55980</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7593,35 +7582,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7629,10 +7618,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317031</v>
+        <v>316961</v>
       </c>
       <c r="R54" t="n">
-        <v>6567009</v>
+        <v>6566845</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7667,11 +7656,6 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7683,7 +7667,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7701,10 +7685,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113244505</v>
+        <v>113244911</v>
       </c>
       <c r="B55" t="n">
-        <v>89165</v>
+        <v>90083</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7717,21 +7701,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7748,10 +7732,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316987</v>
+        <v>316924</v>
       </c>
       <c r="R55" t="n">
-        <v>6566830</v>
+        <v>6567085</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7798,22 +7782,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7831,10 +7815,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113244911</v>
+        <v>113246509</v>
       </c>
       <c r="B56" t="n">
-        <v>90083</v>
+        <v>55988</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7843,34 +7827,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7878,10 +7871,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316924</v>
+        <v>316984</v>
       </c>
       <c r="R56" t="n">
-        <v>6567085</v>
+        <v>6566956</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7922,28 +7915,12 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Låga # Picea abies</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7961,10 +7938,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113245616</v>
+        <v>113246434</v>
       </c>
       <c r="B57" t="n">
-        <v>90530</v>
+        <v>56769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7977,30 +7954,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1213</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8008,10 +7994,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316848</v>
+        <v>317072</v>
       </c>
       <c r="R57" t="n">
-        <v>6567253</v>
+        <v>6566964</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8052,7 +8038,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -8063,17 +8048,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8091,10 +8076,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113244952</v>
+        <v>113252817</v>
       </c>
       <c r="B58" t="n">
-        <v>91367</v>
+        <v>90008</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8107,21 +8092,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8142,10 +8127,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317047</v>
+        <v>316989</v>
       </c>
       <c r="R58" t="n">
-        <v>6567067</v>
+        <v>6567074</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8193,6 +8178,21 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B59" t="n">
-        <v>8432</v>
+        <v>90308</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,36 +8222,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8259,10 +8257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R59" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8342,10 +8340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B60" t="n">
-        <v>90302</v>
+        <v>8432</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8354,34 +8352,36 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R60" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335725</v>
+        <v>113335903</v>
       </c>
       <c r="B61" t="n">
-        <v>89658</v>
+        <v>91532</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>937</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317054</v>
+        <v>317062</v>
       </c>
       <c r="R61" t="n">
-        <v>6566709</v>
+        <v>6566632</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,22 +8569,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113335903</v>
+        <v>113335725</v>
       </c>
       <c r="B62" t="n">
-        <v>91532</v>
+        <v>89658</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>937</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317062</v>
+        <v>317054</v>
       </c>
       <c r="R62" t="n">
-        <v>6566632</v>
+        <v>6566709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8699,22 +8699,22 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
         <v>113338739</v>
       </c>
       <c r="B65" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>113338079</v>
       </c>
       <c r="B66" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>113338164</v>
       </c>
       <c r="B67" t="n">
-        <v>55988</v>
+        <v>55992</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378352</v>
+        <v>113378172</v>
       </c>
       <c r="B68" t="n">
-        <v>5163</v>
+        <v>89664</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,32 +9391,30 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102204</v>
+        <v>937</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9424,10 +9422,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316796</v>
+        <v>316763</v>
       </c>
       <c r="R68" t="n">
-        <v>6566783</v>
+        <v>6566812</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9479,17 +9477,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9507,10 +9505,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378820</v>
+        <v>113378087</v>
       </c>
       <c r="B69" t="n">
-        <v>94908</v>
+        <v>90694</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9523,31 +9521,30 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>5454</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9555,10 +9552,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316796</v>
+        <v>316719</v>
       </c>
       <c r="R69" t="n">
-        <v>6567088</v>
+        <v>6566788</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9602,6 +9599,26 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9618,10 +9635,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378411</v>
+        <v>113378352</v>
       </c>
       <c r="B70" t="n">
-        <v>4990</v>
+        <v>5163</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9634,21 +9651,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105212</v>
+        <v>102204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9667,10 +9684,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316861</v>
+        <v>316796</v>
       </c>
       <c r="R70" t="n">
-        <v>6566893</v>
+        <v>6566783</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9732,7 +9749,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9750,10 +9767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378172</v>
+        <v>113378774</v>
       </c>
       <c r="B71" t="n">
-        <v>89658</v>
+        <v>94914</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9766,30 +9783,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9797,10 +9815,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316763</v>
+        <v>316837</v>
       </c>
       <c r="R71" t="n">
-        <v>6566812</v>
+        <v>6566820</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9852,17 +9870,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9880,10 +9898,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113377981</v>
+        <v>113377913</v>
       </c>
       <c r="B72" t="n">
-        <v>90343</v>
+        <v>94914</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9896,30 +9914,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9927,10 +9946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316671</v>
+        <v>316859</v>
       </c>
       <c r="R72" t="n">
-        <v>6566772</v>
+        <v>6566682</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9982,17 +10001,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10010,10 +10029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113377913</v>
+        <v>113378820</v>
       </c>
       <c r="B73" t="n">
-        <v>94908</v>
+        <v>94914</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10058,10 +10077,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316859</v>
+        <v>316796</v>
       </c>
       <c r="R73" t="n">
-        <v>6566682</v>
+        <v>6567088</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10105,26 +10124,6 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -10141,10 +10140,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378715</v>
+        <v>113378364</v>
       </c>
       <c r="B74" t="n">
-        <v>90302</v>
+        <v>94914</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10153,34 +10152,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10188,10 +10188,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316843</v>
+        <v>316813</v>
       </c>
       <c r="R74" t="n">
-        <v>6567058</v>
+        <v>6566808</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378774</v>
+        <v>113378411</v>
       </c>
       <c r="B75" t="n">
-        <v>94908</v>
+        <v>4990</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10287,31 +10287,32 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10319,10 +10320,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316837</v>
+        <v>316861</v>
       </c>
       <c r="R75" t="n">
-        <v>6566820</v>
+        <v>6566893</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10374,17 +10375,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10402,10 +10403,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378087</v>
+        <v>113377981</v>
       </c>
       <c r="B76" t="n">
-        <v>90688</v>
+        <v>90349</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10418,21 +10419,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5454</v>
+        <v>73</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10449,10 +10450,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316719</v>
+        <v>316671</v>
       </c>
       <c r="R76" t="n">
-        <v>6566788</v>
+        <v>6566772</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10504,17 +10505,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10532,10 +10533,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378035</v>
+        <v>113378715</v>
       </c>
       <c r="B77" t="n">
-        <v>94908</v>
+        <v>90308</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10544,35 +10545,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10580,10 +10580,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316688</v>
+        <v>316843</v>
       </c>
       <c r="R77" t="n">
-        <v>6566808</v>
+        <v>6567058</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10663,10 +10663,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113377902</v>
+        <v>113378035</v>
       </c>
       <c r="B78" t="n">
-        <v>94908</v>
+        <v>94914</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316879</v>
+        <v>316688</v>
       </c>
       <c r="R78" t="n">
-        <v>6566606</v>
+        <v>6566808</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10794,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378364</v>
+        <v>113377902</v>
       </c>
       <c r="B79" t="n">
-        <v>94908</v>
+        <v>94914</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316813</v>
+        <v>316879</v>
       </c>
       <c r="R79" t="n">
-        <v>6566808</v>
+        <v>6566606</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113405679</v>
+        <v>113427239</v>
       </c>
       <c r="B81" t="n">
-        <v>43542</v>
+        <v>90542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11067,36 +11067,34 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>101735</v>
+        <v>5467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11104,10 +11102,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316567</v>
+        <v>316795</v>
       </c>
       <c r="R81" t="n">
-        <v>6566848</v>
+        <v>6567015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11134,12 +11132,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11154,22 +11152,22 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11187,10 +11185,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113427288</v>
+        <v>113427359</v>
       </c>
       <c r="B82" t="n">
-        <v>90302</v>
+        <v>94908</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11199,34 +11197,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11234,10 +11233,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316863</v>
+        <v>316843</v>
       </c>
       <c r="R82" t="n">
-        <v>6567163</v>
+        <v>6567130</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11317,10 +11316,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113427239</v>
+        <v>113427288</v>
       </c>
       <c r="B83" t="n">
-        <v>90542</v>
+        <v>90302</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11329,25 +11328,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5467</v>
+        <v>5260</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11364,10 +11363,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316795</v>
+        <v>316863</v>
       </c>
       <c r="R83" t="n">
-        <v>6567015</v>
+        <v>6567163</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11447,10 +11446,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427359</v>
+        <v>113406315</v>
       </c>
       <c r="B84" t="n">
-        <v>94908</v>
+        <v>90008</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11463,31 +11462,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11495,10 +11497,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316843</v>
+        <v>316935</v>
       </c>
       <c r="R84" t="n">
-        <v>6567130</v>
+        <v>6566886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11525,12 +11527,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11545,7 +11547,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11560,7 +11562,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11578,10 +11580,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113406315</v>
+        <v>113405679</v>
       </c>
       <c r="B85" t="n">
-        <v>90008</v>
+        <v>43542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11590,38 +11592,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316935</v>
+        <v>316567</v>
       </c>
       <c r="R85" t="n">
-        <v>6566886</v>
+        <v>6566848</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11679,22 +11679,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B90" t="n">
-        <v>89658</v>
+        <v>90236</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R90" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,26 +12328,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12364,10 +12344,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B91" t="n">
-        <v>90236</v>
+        <v>89658</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12376,25 +12356,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12411,10 +12391,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R91" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12458,6 +12438,26 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90485</v>
+        <v>90491</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113245442</v>
+        <v>113246509</v>
       </c>
       <c r="B43" t="n">
-        <v>90542</v>
+        <v>55992</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6161,34 +6161,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5467</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6196,10 +6205,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316848</v>
+        <v>316984</v>
       </c>
       <c r="R43" t="n">
-        <v>6567253</v>
+        <v>6566956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6240,28 +6249,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6279,10 +6272,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113245616</v>
+        <v>113244725</v>
       </c>
       <c r="B44" t="n">
-        <v>90530</v>
+        <v>90836</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6291,25 +6284,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1213</v>
+        <v>1975</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6326,10 +6319,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316848</v>
+        <v>317004</v>
       </c>
       <c r="R44" t="n">
-        <v>6567253</v>
+        <v>6566831</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6376,7 +6369,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6409,10 +6402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113245002</v>
+        <v>113245476</v>
       </c>
       <c r="B45" t="n">
-        <v>89165</v>
+        <v>90548</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6425,21 +6418,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>5467</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6456,10 +6449,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317012</v>
+        <v>316848</v>
       </c>
       <c r="R45" t="n">
-        <v>6566822</v>
+        <v>6567253</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6506,7 +6499,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6539,10 +6532,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113244505</v>
+        <v>113245823</v>
       </c>
       <c r="B46" t="n">
-        <v>89165</v>
+        <v>90694</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6555,21 +6548,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>5454</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6586,10 +6579,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316987</v>
+        <v>316794</v>
       </c>
       <c r="R46" t="n">
-        <v>6566830</v>
+        <v>6567127</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6636,7 +6629,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6669,10 +6662,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113244003</v>
+        <v>113245616</v>
       </c>
       <c r="B47" t="n">
-        <v>91532</v>
+        <v>90536</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6685,21 +6678,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>1213</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6716,10 +6709,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316970</v>
+        <v>316848</v>
       </c>
       <c r="R47" t="n">
-        <v>6566774</v>
+        <v>6567253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6781,7 +6774,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6799,10 +6792,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113243787</v>
+        <v>113244003</v>
       </c>
       <c r="B48" t="n">
-        <v>90094</v>
+        <v>91538</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6811,32 +6804,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6850,10 +6839,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316816</v>
+        <v>316970</v>
       </c>
       <c r="R48" t="n">
-        <v>6566787</v>
+        <v>6566774</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6905,17 +6894,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6933,10 +6922,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244782</v>
+        <v>113244952</v>
       </c>
       <c r="B49" t="n">
-        <v>89165</v>
+        <v>91373</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6949,24 +6938,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6980,10 +6973,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316904</v>
+        <v>317047</v>
       </c>
       <c r="R49" t="n">
-        <v>6567084</v>
+        <v>6567067</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7031,21 +7024,6 @@
       <c r="AI49" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7063,10 +7041,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113245823</v>
+        <v>113246470</v>
       </c>
       <c r="B50" t="n">
-        <v>90688</v>
+        <v>56918</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7079,30 +7057,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5454</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7110,10 +7093,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>316794</v>
+        <v>317031</v>
       </c>
       <c r="R50" t="n">
-        <v>6567127</v>
+        <v>6567009</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7148,34 +7131,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7193,10 +7165,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113244952</v>
+        <v>113252817</v>
       </c>
       <c r="B51" t="n">
-        <v>91367</v>
+        <v>90014</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7209,21 +7181,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7244,10 +7216,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317047</v>
+        <v>316989</v>
       </c>
       <c r="R51" t="n">
-        <v>6567067</v>
+        <v>6567074</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7295,6 +7267,21 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7312,10 +7299,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113246470</v>
+        <v>113244911</v>
       </c>
       <c r="B52" t="n">
-        <v>56914</v>
+        <v>90089</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7328,35 +7315,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7364,10 +7346,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317031</v>
+        <v>316924</v>
       </c>
       <c r="R52" t="n">
-        <v>6567009</v>
+        <v>6567085</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7402,23 +7384,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7436,10 +7429,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113244725</v>
+        <v>113244505</v>
       </c>
       <c r="B53" t="n">
-        <v>90830</v>
+        <v>89171</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7448,25 +7441,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1975</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7483,10 +7476,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317004</v>
+        <v>316987</v>
       </c>
       <c r="R53" t="n">
-        <v>6566831</v>
+        <v>6566830</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7566,10 +7559,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113246404</v>
+        <v>113244782</v>
       </c>
       <c r="B54" t="n">
-        <v>55980</v>
+        <v>89171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7582,35 +7575,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7618,10 +7606,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316961</v>
+        <v>316904</v>
       </c>
       <c r="R54" t="n">
-        <v>6566845</v>
+        <v>6567084</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7662,12 +7650,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7685,10 +7689,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113244911</v>
+        <v>113243787</v>
       </c>
       <c r="B55" t="n">
-        <v>90083</v>
+        <v>90100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7697,28 +7701,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7732,10 +7740,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316924</v>
+        <v>316816</v>
       </c>
       <c r="R55" t="n">
-        <v>6567085</v>
+        <v>6566787</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7782,22 +7790,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7815,10 +7823,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113246509</v>
+        <v>113246434</v>
       </c>
       <c r="B56" t="n">
-        <v>55988</v>
+        <v>56773</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7827,30 +7835,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -7861,7 +7869,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7871,10 +7879,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316984</v>
+        <v>317072</v>
       </c>
       <c r="R56" t="n">
-        <v>6566956</v>
+        <v>6566964</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7921,6 +7929,21 @@
       <c r="AI56" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7938,10 +7961,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113246434</v>
+        <v>113245002</v>
       </c>
       <c r="B57" t="n">
-        <v>56769</v>
+        <v>89171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7954,39 +7977,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7994,10 +8008,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317072</v>
+        <v>317012</v>
       </c>
       <c r="R57" t="n">
-        <v>6566964</v>
+        <v>6566822</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8038,27 +8052,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8076,10 +8091,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113252817</v>
+        <v>113246404</v>
       </c>
       <c r="B58" t="n">
-        <v>90008</v>
+        <v>55984</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8092,21 +8107,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8114,12 +8129,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8127,10 +8143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>316989</v>
+        <v>316961</v>
       </c>
       <c r="R58" t="n">
-        <v>6567074</v>
+        <v>6566845</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8171,28 +8187,12 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8475,7 +8475,7 @@
         <v>113335903</v>
       </c>
       <c r="B61" t="n">
-        <v>91532</v>
+        <v>91538</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113335725</v>
+        <v>113336300</v>
       </c>
       <c r="B62" t="n">
-        <v>89658</v>
+        <v>90014</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>937</v>
+        <v>3242</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317054</v>
+        <v>317034</v>
       </c>
       <c r="R62" t="n">
-        <v>6566709</v>
+        <v>6566659</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8704,17 +8704,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113336300</v>
+        <v>113335687</v>
       </c>
       <c r="B63" t="n">
-        <v>90008</v>
+        <v>89171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317034</v>
+        <v>317131</v>
       </c>
       <c r="R63" t="n">
-        <v>6566659</v>
+        <v>6566427</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335687</v>
+        <v>113335725</v>
       </c>
       <c r="B64" t="n">
-        <v>89165</v>
+        <v>89664</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>937</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317131</v>
+        <v>317054</v>
       </c>
       <c r="R64" t="n">
-        <v>6566427</v>
+        <v>6566709</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,22 +8959,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90302</v>
+        <v>90308</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427239</v>
+        <v>113406315</v>
       </c>
       <c r="B81" t="n">
-        <v>90542</v>
+        <v>90014</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11071,24 +11071,28 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5467</v>
+        <v>3242</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11102,10 +11106,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316795</v>
+        <v>316935</v>
       </c>
       <c r="R81" t="n">
-        <v>6567015</v>
+        <v>6566886</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11132,12 +11136,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11152,7 +11156,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11167,7 +11171,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11185,10 +11189,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113427359</v>
+        <v>113427288</v>
       </c>
       <c r="B82" t="n">
-        <v>94908</v>
+        <v>90308</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11197,35 +11201,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11233,10 +11236,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316843</v>
+        <v>316863</v>
       </c>
       <c r="R82" t="n">
-        <v>6567130</v>
+        <v>6567163</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11316,10 +11319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113427288</v>
+        <v>113405679</v>
       </c>
       <c r="B83" t="n">
-        <v>90302</v>
+        <v>43543</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11328,34 +11331,36 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11363,10 +11368,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316863</v>
+        <v>316567</v>
       </c>
       <c r="R83" t="n">
-        <v>6567163</v>
+        <v>6566848</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11393,12 +11398,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11413,22 +11418,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11446,10 +11451,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113406315</v>
+        <v>113427359</v>
       </c>
       <c r="B84" t="n">
-        <v>90008</v>
+        <v>94914</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11462,34 +11467,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3242</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11497,10 +11499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316935</v>
+        <v>316843</v>
       </c>
       <c r="R84" t="n">
-        <v>6566886</v>
+        <v>6567130</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11527,12 +11529,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11547,7 +11549,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11562,7 +11564,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11580,10 +11582,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113405679</v>
+        <v>113427239</v>
       </c>
       <c r="B85" t="n">
-        <v>43542</v>
+        <v>90548</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11592,36 +11594,34 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>101735</v>
+        <v>5467</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316567</v>
+        <v>316795</v>
       </c>
       <c r="R85" t="n">
-        <v>6566848</v>
+        <v>6567015</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11679,22 +11679,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
         <v>113405650</v>
       </c>
       <c r="B86" t="n">
-        <v>43542</v>
+        <v>43543</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>113245275</v>
       </c>
       <c r="B90" t="n">
-        <v>90236</v>
+        <v>90242</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>113245353</v>
       </c>
       <c r="B91" t="n">
-        <v>89658</v>
+        <v>89664</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90530</v>
+        <v>90536</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113246509</v>
+        <v>113244725</v>
       </c>
       <c r="B43" t="n">
-        <v>55992</v>
+        <v>90836</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6161,43 +6161,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1975</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Kauffman) Jülich</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6205,10 +6196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>316984</v>
+        <v>317004</v>
       </c>
       <c r="R43" t="n">
-        <v>6566956</v>
+        <v>6566831</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6249,12 +6240,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6272,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113244725</v>
+        <v>113246404</v>
       </c>
       <c r="B44" t="n">
-        <v>90836</v>
+        <v>55984</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6284,34 +6291,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1975</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6319,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317004</v>
+        <v>316961</v>
       </c>
       <c r="R44" t="n">
-        <v>6566831</v>
+        <v>6566845</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6363,28 +6375,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6402,10 +6398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113245476</v>
+        <v>113252817</v>
       </c>
       <c r="B45" t="n">
-        <v>90548</v>
+        <v>90014</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6418,24 +6414,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5467</v>
+        <v>3242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>316848</v>
+        <v>316989</v>
       </c>
       <c r="R45" t="n">
-        <v>6567253</v>
+        <v>6567074</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6532,10 +6532,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113245823</v>
+        <v>113246509</v>
       </c>
       <c r="B46" t="n">
-        <v>90694</v>
+        <v>55992</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6544,34 +6544,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5454</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6579,10 +6588,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316794</v>
+        <v>316984</v>
       </c>
       <c r="R46" t="n">
-        <v>6567127</v>
+        <v>6566956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6623,28 +6632,12 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6662,10 +6655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113245616</v>
+        <v>113244952</v>
       </c>
       <c r="B47" t="n">
-        <v>90536</v>
+        <v>91373</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6678,24 +6671,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1213</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6709,10 +6706,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316848</v>
+        <v>317047</v>
       </c>
       <c r="R47" t="n">
-        <v>6567253</v>
+        <v>6567067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6760,21 +6757,6 @@
       <c r="AI47" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6792,10 +6774,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113244003</v>
+        <v>113243787</v>
       </c>
       <c r="B48" t="n">
-        <v>91538</v>
+        <v>90100</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6804,28 +6786,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>1205</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6839,10 +6825,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316970</v>
+        <v>316816</v>
       </c>
       <c r="R48" t="n">
-        <v>6566774</v>
+        <v>6566787</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6894,17 +6880,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6922,10 +6908,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113244952</v>
+        <v>113245616</v>
       </c>
       <c r="B49" t="n">
-        <v>91373</v>
+        <v>90536</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6938,28 +6924,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>1213</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6973,10 +6955,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>317047</v>
+        <v>316848</v>
       </c>
       <c r="R49" t="n">
-        <v>6567067</v>
+        <v>6567253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7024,6 +7006,21 @@
       <c r="AI49" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7041,10 +7038,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113246470</v>
+        <v>113245002</v>
       </c>
       <c r="B50" t="n">
-        <v>56918</v>
+        <v>89171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7057,35 +7054,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7093,10 +7085,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>317031</v>
+        <v>317012</v>
       </c>
       <c r="R50" t="n">
-        <v>6567009</v>
+        <v>6566822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7131,23 +7123,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7165,10 +7168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113252817</v>
+        <v>113246434</v>
       </c>
       <c r="B51" t="n">
-        <v>90014</v>
+        <v>56773</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7181,21 +7184,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7203,12 +7206,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7216,10 +7224,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>316989</v>
+        <v>317072</v>
       </c>
       <c r="R51" t="n">
-        <v>6567074</v>
+        <v>6566964</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7260,7 +7268,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7271,17 +7278,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7299,10 +7306,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113244911</v>
+        <v>113245442</v>
       </c>
       <c r="B52" t="n">
-        <v>90089</v>
+        <v>90548</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7315,21 +7322,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7346,10 +7353,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316924</v>
+        <v>316848</v>
       </c>
       <c r="R52" t="n">
-        <v>6567085</v>
+        <v>6567253</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7396,22 +7403,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7429,10 +7436,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113244505</v>
+        <v>113245823</v>
       </c>
       <c r="B53" t="n">
-        <v>89171</v>
+        <v>90694</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7445,21 +7452,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>5454</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7476,10 +7483,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316987</v>
+        <v>316794</v>
       </c>
       <c r="R53" t="n">
-        <v>6566830</v>
+        <v>6567127</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7526,7 +7533,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7559,10 +7566,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113244782</v>
+        <v>113244003</v>
       </c>
       <c r="B54" t="n">
-        <v>89171</v>
+        <v>91538</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7575,21 +7582,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7606,10 +7613,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>316904</v>
+        <v>316970</v>
       </c>
       <c r="R54" t="n">
-        <v>6567084</v>
+        <v>6566774</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7671,7 +7678,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7689,10 +7696,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113243787</v>
+        <v>113244911</v>
       </c>
       <c r="B55" t="n">
-        <v>90100</v>
+        <v>90089</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7701,32 +7708,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7740,10 +7743,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316816</v>
+        <v>316924</v>
       </c>
       <c r="R55" t="n">
-        <v>6566787</v>
+        <v>6567085</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7790,22 +7793,22 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7823,10 +7826,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113246434</v>
+        <v>113244782</v>
       </c>
       <c r="B56" t="n">
-        <v>56773</v>
+        <v>89171</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7839,39 +7842,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7879,10 +7873,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317072</v>
+        <v>316904</v>
       </c>
       <c r="R56" t="n">
-        <v>6566964</v>
+        <v>6567084</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7923,6 +7917,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7933,17 +7928,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7961,7 +7956,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113245002</v>
+        <v>113244505</v>
       </c>
       <c r="B57" t="n">
         <v>89171</v>
@@ -8008,10 +8003,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317012</v>
+        <v>316987</v>
       </c>
       <c r="R57" t="n">
-        <v>6566822</v>
+        <v>6566830</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8091,10 +8086,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113246404</v>
+        <v>113246470</v>
       </c>
       <c r="B58" t="n">
-        <v>55984</v>
+        <v>56918</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8107,35 +8102,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8143,10 +8138,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>316961</v>
+        <v>317031</v>
       </c>
       <c r="R58" t="n">
-        <v>6566845</v>
+        <v>6567009</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8181,6 +8176,11 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B59" t="n">
-        <v>90308</v>
+        <v>8432</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,34 +8222,36 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8257,10 +8259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R59" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8340,10 +8342,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B60" t="n">
-        <v>8432</v>
+        <v>90308</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8352,36 +8354,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R60" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335903</v>
+        <v>113336300</v>
       </c>
       <c r="B61" t="n">
-        <v>91538</v>
+        <v>90014</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317062</v>
+        <v>317034</v>
       </c>
       <c r="R61" t="n">
-        <v>6566632</v>
+        <v>6566659</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113336300</v>
+        <v>113335687</v>
       </c>
       <c r="B62" t="n">
-        <v>90014</v>
+        <v>89171</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317034</v>
+        <v>317131</v>
       </c>
       <c r="R62" t="n">
-        <v>6566659</v>
+        <v>6566427</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113335687</v>
+        <v>113335725</v>
       </c>
       <c r="B63" t="n">
-        <v>89171</v>
+        <v>89664</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>937</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317131</v>
+        <v>317054</v>
       </c>
       <c r="R63" t="n">
-        <v>6566427</v>
+        <v>6566709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8829,22 +8829,22 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335725</v>
+        <v>113335903</v>
       </c>
       <c r="B64" t="n">
-        <v>89664</v>
+        <v>91538</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>937</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317054</v>
+        <v>317062</v>
       </c>
       <c r="R64" t="n">
-        <v>6566709</v>
+        <v>6566632</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,22 +8959,22 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B65" t="n">
-        <v>78164</v>
+        <v>55992</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,34 +9004,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9039,10 +9048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R65" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9083,28 +9092,12 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9252,10 +9245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338164</v>
+        <v>113338739</v>
       </c>
       <c r="B67" t="n">
-        <v>55992</v>
+        <v>78164</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9264,43 +9257,34 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9308,10 +9292,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317128</v>
+        <v>317102</v>
       </c>
       <c r="R67" t="n">
-        <v>6566863</v>
+        <v>6566586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9352,12 +9336,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378172</v>
+        <v>113377981</v>
       </c>
       <c r="B68" t="n">
-        <v>89664</v>
+        <v>90349</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>937</v>
+        <v>73</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9422,10 +9422,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316763</v>
+        <v>316671</v>
       </c>
       <c r="R68" t="n">
-        <v>6566812</v>
+        <v>6566772</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9505,10 +9505,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378087</v>
+        <v>113377913</v>
       </c>
       <c r="B69" t="n">
-        <v>90694</v>
+        <v>94914</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9521,30 +9521,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5454</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9552,10 +9553,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316719</v>
+        <v>316859</v>
       </c>
       <c r="R69" t="n">
-        <v>6566788</v>
+        <v>6566682</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9607,17 +9608,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9635,10 +9636,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378352</v>
+        <v>113378087</v>
       </c>
       <c r="B70" t="n">
-        <v>5163</v>
+        <v>90694</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9651,32 +9652,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102204</v>
+        <v>5454</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9684,10 +9683,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316796</v>
+        <v>316719</v>
       </c>
       <c r="R70" t="n">
-        <v>6566783</v>
+        <v>6566788</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9739,17 +9738,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9767,10 +9766,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378774</v>
+        <v>113378411</v>
       </c>
       <c r="B71" t="n">
-        <v>94914</v>
+        <v>4990</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9783,31 +9782,32 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316837</v>
+        <v>316861</v>
       </c>
       <c r="R71" t="n">
-        <v>6566820</v>
+        <v>6566893</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9870,17 +9870,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113377913</v>
+        <v>113378172</v>
       </c>
       <c r="B72" t="n">
-        <v>94914</v>
+        <v>89664</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9914,31 +9914,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>937</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9946,10 +9945,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316859</v>
+        <v>316763</v>
       </c>
       <c r="R72" t="n">
-        <v>6566682</v>
+        <v>6566812</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10001,17 +10000,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10029,7 +10028,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378820</v>
+        <v>113378774</v>
       </c>
       <c r="B73" t="n">
         <v>94914</v>
@@ -10077,10 +10076,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316796</v>
+        <v>316837</v>
       </c>
       <c r="R73" t="n">
-        <v>6567088</v>
+        <v>6566820</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10124,6 +10123,26 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -10271,10 +10290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378411</v>
+        <v>113378715</v>
       </c>
       <c r="B75" t="n">
-        <v>4990</v>
+        <v>90308</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10283,36 +10302,34 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105212</v>
+        <v>5260</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10320,10 +10337,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316861</v>
+        <v>316843</v>
       </c>
       <c r="R75" t="n">
-        <v>6566893</v>
+        <v>6567058</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10375,17 +10392,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10403,10 +10420,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113377981</v>
+        <v>113378352</v>
       </c>
       <c r="B76" t="n">
-        <v>90349</v>
+        <v>5163</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10419,30 +10436,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>102204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10450,10 +10469,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316671</v>
+        <v>316796</v>
       </c>
       <c r="R76" t="n">
-        <v>6566772</v>
+        <v>6566783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10505,17 +10524,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10533,10 +10552,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378715</v>
+        <v>113378035</v>
       </c>
       <c r="B77" t="n">
-        <v>90308</v>
+        <v>94914</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10545,34 +10564,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10580,10 +10600,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316843</v>
+        <v>316688</v>
       </c>
       <c r="R77" t="n">
-        <v>6567058</v>
+        <v>6566808</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10645,7 +10665,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10663,7 +10683,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113378035</v>
+        <v>113377902</v>
       </c>
       <c r="B78" t="n">
         <v>94914</v>
@@ -10711,10 +10731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316688</v>
+        <v>316879</v>
       </c>
       <c r="R78" t="n">
-        <v>6566808</v>
+        <v>6566606</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10794,7 +10814,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113377902</v>
+        <v>113378820</v>
       </c>
       <c r="B79" t="n">
         <v>94914</v>
@@ -10842,10 +10862,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316879</v>
+        <v>316796</v>
       </c>
       <c r="R79" t="n">
-        <v>6566606</v>
+        <v>6567088</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10889,26 +10909,6 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -11189,10 +11189,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113427288</v>
+        <v>113405650</v>
       </c>
       <c r="B82" t="n">
-        <v>90308</v>
+        <v>43543</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11201,34 +11201,36 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11236,10 +11238,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316863</v>
+        <v>316574</v>
       </c>
       <c r="R82" t="n">
-        <v>6567163</v>
+        <v>6566830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11266,12 +11268,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11286,22 +11288,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11451,10 +11453,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427359</v>
+        <v>113427288</v>
       </c>
       <c r="B84" t="n">
-        <v>94914</v>
+        <v>90308</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11463,35 +11465,34 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11499,10 +11500,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316843</v>
+        <v>316863</v>
       </c>
       <c r="R84" t="n">
-        <v>6567130</v>
+        <v>6567163</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11712,10 +11713,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113405650</v>
+        <v>113427359</v>
       </c>
       <c r="B86" t="n">
-        <v>43543</v>
+        <v>94914</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11724,36 +11725,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316574</v>
+        <v>316843</v>
       </c>
       <c r="R86" t="n">
-        <v>6566830</v>
+        <v>6567130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11791,12 +11791,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11811,22 +11811,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B90" t="n">
-        <v>90242</v>
+        <v>89664</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R90" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,6 +12328,26 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12344,10 +12364,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B91" t="n">
-        <v>89664</v>
+        <v>90242</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12356,25 +12376,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12391,10 +12411,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R91" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12438,26 +12458,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6532,10 +6532,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113246509</v>
+        <v>113243787</v>
       </c>
       <c r="B46" t="n">
-        <v>55992</v>
+        <v>90100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6548,39 +6548,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6588,10 +6583,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316984</v>
+        <v>316816</v>
       </c>
       <c r="R46" t="n">
-        <v>6566956</v>
+        <v>6566787</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6632,12 +6627,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6655,10 +6666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113244952</v>
+        <v>113246509</v>
       </c>
       <c r="B47" t="n">
-        <v>91373</v>
+        <v>55992</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6667,38 +6678,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6706,10 +6722,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317047</v>
+        <v>316984</v>
       </c>
       <c r="R47" t="n">
-        <v>6567067</v>
+        <v>6566956</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6750,7 +6766,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6774,10 +6789,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113243787</v>
+        <v>113244952</v>
       </c>
       <c r="B48" t="n">
-        <v>90100</v>
+        <v>91373</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6786,25 +6801,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6825,10 +6840,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>316816</v>
+        <v>317047</v>
       </c>
       <c r="R48" t="n">
-        <v>6566787</v>
+        <v>6567067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6876,21 +6891,6 @@
       <c r="AI48" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -6149,10 +6149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113244725</v>
+        <v>113244952</v>
       </c>
       <c r="B43" t="n">
-        <v>90836</v>
+        <v>91380</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6161,28 +6161,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1975</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6196,10 +6200,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317004</v>
+        <v>317047</v>
       </c>
       <c r="R43" t="n">
-        <v>6566831</v>
+        <v>6567067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6246,22 +6250,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6279,10 +6268,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113246404</v>
+        <v>113244505</v>
       </c>
       <c r="B44" t="n">
-        <v>55984</v>
+        <v>89178</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6295,35 +6284,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6331,10 +6315,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>316961</v>
+        <v>316987</v>
       </c>
       <c r="R44" t="n">
-        <v>6566845</v>
+        <v>6566830</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6375,12 +6359,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Tallskogm mosskant</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113252817</v>
+        <v>113246434</v>
       </c>
       <c r="B45" t="n">
-        <v>90014</v>
+        <v>56780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6414,21 +6414,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6436,12 +6436,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6449,10 +6454,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>316989</v>
+        <v>317072</v>
       </c>
       <c r="R45" t="n">
-        <v>6567074</v>
+        <v>6566964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6493,7 +6498,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6504,17 +6508,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6532,10 +6536,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113243787</v>
+        <v>113244782</v>
       </c>
       <c r="B46" t="n">
-        <v>90100</v>
+        <v>89178</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6544,32 +6548,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1205</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>316816</v>
+        <v>316904</v>
       </c>
       <c r="R46" t="n">
-        <v>6566787</v>
+        <v>6567084</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6638,17 +6638,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Levande träd # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113246509</v>
+        <v>113244725</v>
       </c>
       <c r="B47" t="n">
-        <v>55992</v>
+        <v>90843</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6678,43 +6678,34 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>1975</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Kauffman) Jülich</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6722,10 +6713,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>316984</v>
+        <v>317004</v>
       </c>
       <c r="R47" t="n">
-        <v>6566956</v>
+        <v>6566831</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6766,12 +6757,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6789,10 +6796,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113244952</v>
+        <v>113243787</v>
       </c>
       <c r="B48" t="n">
-        <v>91373</v>
+        <v>90107</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6801,25 +6808,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>1205</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6840,10 +6847,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>317047</v>
+        <v>316816</v>
       </c>
       <c r="R48" t="n">
-        <v>6567067</v>
+        <v>6566787</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6891,6 +6898,21 @@
       <c r="AI48" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Levande träd # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6908,10 +6930,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113245616</v>
+        <v>113245823</v>
       </c>
       <c r="B49" t="n">
-        <v>90536</v>
+        <v>90701</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6924,21 +6946,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1213</v>
+        <v>5454</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6955,10 +6977,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>316848</v>
+        <v>316794</v>
       </c>
       <c r="R49" t="n">
-        <v>6567253</v>
+        <v>6567127</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7038,10 +7060,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113245002</v>
+        <v>113246509</v>
       </c>
       <c r="B50" t="n">
-        <v>89171</v>
+        <v>55999</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7050,34 +7072,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7085,10 +7116,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>317012</v>
+        <v>316984</v>
       </c>
       <c r="R50" t="n">
-        <v>6566822</v>
+        <v>6566956</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7129,28 +7160,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7168,10 +7183,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113246434</v>
+        <v>113245476</v>
       </c>
       <c r="B51" t="n">
-        <v>56773</v>
+        <v>90555</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7184,39 +7199,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5467</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7224,10 +7230,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317072</v>
+        <v>316848</v>
       </c>
       <c r="R51" t="n">
-        <v>6566964</v>
+        <v>6567253</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7268,6 +7274,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7278,17 +7285,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7306,10 +7313,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113245442</v>
+        <v>113245002</v>
       </c>
       <c r="B52" t="n">
-        <v>90548</v>
+        <v>89178</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7322,21 +7329,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7353,10 +7360,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>316848</v>
+        <v>317012</v>
       </c>
       <c r="R52" t="n">
-        <v>6567253</v>
+        <v>6566822</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7403,7 +7410,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7436,10 +7443,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113245823</v>
+        <v>113245616</v>
       </c>
       <c r="B53" t="n">
-        <v>90694</v>
+        <v>90543</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7452,21 +7459,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5454</v>
+        <v>1213</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7483,10 +7490,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>316794</v>
+        <v>316848</v>
       </c>
       <c r="R53" t="n">
-        <v>6567127</v>
+        <v>6567253</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7569,7 +7576,7 @@
         <v>113244003</v>
       </c>
       <c r="B54" t="n">
-        <v>91538</v>
+        <v>91545</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7696,10 +7703,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113244911</v>
+        <v>113246470</v>
       </c>
       <c r="B55" t="n">
-        <v>90089</v>
+        <v>56925</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7712,30 +7719,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7743,10 +7755,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>316924</v>
+        <v>317031</v>
       </c>
       <c r="R55" t="n">
-        <v>6567085</v>
+        <v>6567009</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7781,34 +7793,23 @@
           <t>2023-11-13</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I mesflock</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Låga # Picea abies</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7826,10 +7827,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113244782</v>
+        <v>113246404</v>
       </c>
       <c r="B56" t="n">
-        <v>89171</v>
+        <v>55991</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7842,30 +7843,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7873,10 +7879,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>316904</v>
+        <v>316961</v>
       </c>
       <c r="R56" t="n">
-        <v>6567084</v>
+        <v>6566845</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7917,28 +7923,12 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Tallskogm mosskant</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7956,10 +7946,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113244505</v>
+        <v>113252817</v>
       </c>
       <c r="B57" t="n">
-        <v>89171</v>
+        <v>90021</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7972,24 +7962,28 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8003,10 +7997,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>316987</v>
+        <v>316989</v>
       </c>
       <c r="R57" t="n">
-        <v>6566830</v>
+        <v>6567074</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8053,7 +8047,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8068,7 +8062,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8086,10 +8080,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113246470</v>
+        <v>113244911</v>
       </c>
       <c r="B58" t="n">
-        <v>56918</v>
+        <v>90096</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8102,35 +8096,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8138,10 +8127,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317031</v>
+        <v>316924</v>
       </c>
       <c r="R58" t="n">
-        <v>6567009</v>
+        <v>6567085</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8176,23 +8165,34 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>I mesflock</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113261989</v>
+        <v>113246376</v>
       </c>
       <c r="B59" t="n">
-        <v>8432</v>
+        <v>90315</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8222,36 +8222,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5260</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8259,10 +8257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317063</v>
+        <v>316798</v>
       </c>
       <c r="R59" t="n">
-        <v>6566798</v>
+        <v>6567086</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8342,10 +8340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113246376</v>
+        <v>113261989</v>
       </c>
       <c r="B60" t="n">
-        <v>90308</v>
+        <v>8432</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8354,34 +8352,36 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>316798</v>
+        <v>317063</v>
       </c>
       <c r="R60" t="n">
-        <v>6567086</v>
+        <v>6566798</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113336300</v>
+        <v>113335725</v>
       </c>
       <c r="B61" t="n">
-        <v>90014</v>
+        <v>89671</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3242</v>
+        <v>937</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317034</v>
+        <v>317054</v>
       </c>
       <c r="R61" t="n">
-        <v>6566659</v>
+        <v>6566709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113335687</v>
+        <v>113336300</v>
       </c>
       <c r="B62" t="n">
-        <v>89171</v>
+        <v>90021</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317131</v>
+        <v>317034</v>
       </c>
       <c r="R62" t="n">
-        <v>6566427</v>
+        <v>6566659</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8732,10 +8732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113335725</v>
+        <v>113335903</v>
       </c>
       <c r="B63" t="n">
-        <v>89664</v>
+        <v>91545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8748,21 +8748,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>937</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317054</v>
+        <v>317062</v>
       </c>
       <c r="R63" t="n">
-        <v>6566709</v>
+        <v>6566632</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8829,22 +8829,22 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335903</v>
+        <v>113335687</v>
       </c>
       <c r="B64" t="n">
-        <v>91538</v>
+        <v>89178</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317062</v>
+        <v>317131</v>
       </c>
       <c r="R64" t="n">
-        <v>6566632</v>
+        <v>6566427</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338164</v>
+        <v>113338739</v>
       </c>
       <c r="B65" t="n">
-        <v>55992</v>
+        <v>78171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,43 +9004,34 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9048,10 +9039,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317128</v>
+        <v>317102</v>
       </c>
       <c r="R65" t="n">
-        <v>6566863</v>
+        <v>6566586</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9092,12 +9083,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9115,10 +9122,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338079</v>
+        <v>113338164</v>
       </c>
       <c r="B66" t="n">
-        <v>56773</v>
+        <v>55999</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9127,33 +9134,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9163,10 +9178,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317148</v>
+        <v>317128</v>
       </c>
       <c r="R66" t="n">
-        <v>6566451</v>
+        <v>6566863</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9213,21 +9228,6 @@
       <c r="AI66" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338739</v>
+        <v>113338079</v>
       </c>
       <c r="B67" t="n">
-        <v>78164</v>
+        <v>56780</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9261,30 +9261,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9292,10 +9293,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317102</v>
+        <v>317148</v>
       </c>
       <c r="R67" t="n">
-        <v>6566586</v>
+        <v>6566451</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9336,28 +9337,27 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113377981</v>
+        <v>113378411</v>
       </c>
       <c r="B68" t="n">
-        <v>90349</v>
+        <v>4990</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,30 +9391,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>73</v>
+        <v>105212</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9422,10 +9424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316671</v>
+        <v>316861</v>
       </c>
       <c r="R68" t="n">
-        <v>6566772</v>
+        <v>6566893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9477,17 +9479,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9505,10 +9507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113377913</v>
+        <v>113378820</v>
       </c>
       <c r="B69" t="n">
-        <v>94914</v>
+        <v>94921</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9553,10 +9555,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316859</v>
+        <v>316796</v>
       </c>
       <c r="R69" t="n">
-        <v>6566682</v>
+        <v>6567088</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9600,26 +9602,6 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9639,7 +9621,7 @@
         <v>113378087</v>
       </c>
       <c r="B70" t="n">
-        <v>90694</v>
+        <v>90701</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9766,10 +9748,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378411</v>
+        <v>113378364</v>
       </c>
       <c r="B71" t="n">
-        <v>4990</v>
+        <v>94921</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9782,32 +9764,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105212</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9815,10 +9796,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316861</v>
+        <v>316813</v>
       </c>
       <c r="R71" t="n">
-        <v>6566893</v>
+        <v>6566808</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9870,17 +9851,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9901,7 +9882,7 @@
         <v>113378172</v>
       </c>
       <c r="B72" t="n">
-        <v>89664</v>
+        <v>89671</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10028,10 +10009,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378774</v>
+        <v>113378352</v>
       </c>
       <c r="B73" t="n">
-        <v>94914</v>
+        <v>5163</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10044,31 +10025,32 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10076,10 +10058,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316837</v>
+        <v>316796</v>
       </c>
       <c r="R73" t="n">
-        <v>6566820</v>
+        <v>6566783</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10131,17 +10113,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10159,10 +10141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378364</v>
+        <v>113377913</v>
       </c>
       <c r="B74" t="n">
-        <v>94914</v>
+        <v>94921</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10207,10 +10189,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316813</v>
+        <v>316859</v>
       </c>
       <c r="R74" t="n">
-        <v>6566808</v>
+        <v>6566682</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10262,17 +10244,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10290,10 +10272,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378715</v>
+        <v>113378774</v>
       </c>
       <c r="B75" t="n">
-        <v>90308</v>
+        <v>94921</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10302,34 +10284,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10337,10 +10320,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316843</v>
+        <v>316837</v>
       </c>
       <c r="R75" t="n">
-        <v>6567058</v>
+        <v>6566820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10402,7 +10385,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10420,10 +10403,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378352</v>
+        <v>113377981</v>
       </c>
       <c r="B76" t="n">
-        <v>5163</v>
+        <v>90356</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10436,32 +10419,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102204</v>
+        <v>73</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10469,10 +10450,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316796</v>
+        <v>316671</v>
       </c>
       <c r="R76" t="n">
-        <v>6566783</v>
+        <v>6566772</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10524,17 +10505,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10552,10 +10533,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378035</v>
+        <v>113378715</v>
       </c>
       <c r="B77" t="n">
-        <v>94914</v>
+        <v>90315</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10564,35 +10545,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10600,10 +10580,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316688</v>
+        <v>316843</v>
       </c>
       <c r="R77" t="n">
-        <v>6566808</v>
+        <v>6567058</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10665,7 +10645,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10686,7 +10666,7 @@
         <v>113377902</v>
       </c>
       <c r="B78" t="n">
-        <v>94914</v>
+        <v>94921</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10814,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378820</v>
+        <v>113378035</v>
       </c>
       <c r="B79" t="n">
-        <v>94914</v>
+        <v>94921</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10862,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316796</v>
+        <v>316688</v>
       </c>
       <c r="R79" t="n">
-        <v>6567088</v>
+        <v>6566808</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10909,6 +10889,26 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90308</v>
+        <v>90315</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113406315</v>
+        <v>113405650</v>
       </c>
       <c r="B81" t="n">
-        <v>90014</v>
+        <v>43548</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11067,38 +11067,36 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11106,10 +11104,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316935</v>
+        <v>316574</v>
       </c>
       <c r="R81" t="n">
-        <v>6566886</v>
+        <v>6566830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11156,22 +11154,22 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11189,10 +11187,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113405650</v>
+        <v>113427239</v>
       </c>
       <c r="B82" t="n">
-        <v>43543</v>
+        <v>90555</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11201,36 +11199,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>5467</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11238,10 +11234,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316574</v>
+        <v>316795</v>
       </c>
       <c r="R82" t="n">
-        <v>6566830</v>
+        <v>6567015</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11268,12 +11264,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11288,22 +11284,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11324,7 +11320,7 @@
         <v>113405679</v>
       </c>
       <c r="B83" t="n">
-        <v>43543</v>
+        <v>43548</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11456,7 +11452,7 @@
         <v>113427288</v>
       </c>
       <c r="B84" t="n">
-        <v>90308</v>
+        <v>90315</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11583,10 +11579,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427239</v>
+        <v>113427359</v>
       </c>
       <c r="B85" t="n">
-        <v>90548</v>
+        <v>94921</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11599,30 +11595,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5467</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11630,10 +11627,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316795</v>
+        <v>316843</v>
       </c>
       <c r="R85" t="n">
-        <v>6567015</v>
+        <v>6567130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11713,10 +11710,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113427359</v>
+        <v>113406315</v>
       </c>
       <c r="B86" t="n">
-        <v>94914</v>
+        <v>90021</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11729,31 +11726,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316843</v>
+        <v>316935</v>
       </c>
       <c r="R86" t="n">
-        <v>6567130</v>
+        <v>6566886</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11791,12 +11791,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12234,10 +12234,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245353</v>
+        <v>113245275</v>
       </c>
       <c r="B90" t="n">
-        <v>89664</v>
+        <v>90249</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12246,25 +12246,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>937</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317172</v>
+        <v>317246</v>
       </c>
       <c r="R90" t="n">
-        <v>6566905</v>
+        <v>6566798</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12328,26 +12328,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12364,10 +12344,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B91" t="n">
-        <v>90242</v>
+        <v>89671</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12376,25 +12356,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12411,10 +12391,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R91" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12458,6 +12438,26 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90536</v>
+        <v>90543</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90491</v>
+        <v>90498</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378411</v>
+        <v>113378820</v>
       </c>
       <c r="B68" t="n">
-        <v>4990</v>
+        <v>94921</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,32 +9391,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>105212</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9424,10 +9423,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316861</v>
+        <v>316796</v>
       </c>
       <c r="R68" t="n">
-        <v>6566893</v>
+        <v>6567088</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9471,26 +9470,6 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Ståande torrträd # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9507,10 +9486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378820</v>
+        <v>113378087</v>
       </c>
       <c r="B69" t="n">
-        <v>94921</v>
+        <v>90701</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9523,31 +9502,30 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>5454</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9555,10 +9533,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316796</v>
+        <v>316719</v>
       </c>
       <c r="R69" t="n">
-        <v>6567088</v>
+        <v>6566788</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9602,6 +9580,26 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9618,10 +9616,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378087</v>
+        <v>113378411</v>
       </c>
       <c r="B70" t="n">
-        <v>90701</v>
+        <v>4990</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9634,30 +9632,32 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5454</v>
+        <v>105212</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9665,10 +9665,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316719</v>
+        <v>316861</v>
       </c>
       <c r="R70" t="n">
-        <v>6566788</v>
+        <v>6566893</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9720,17 +9720,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -8472,10 +8472,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113335725</v>
+        <v>113335687</v>
       </c>
       <c r="B61" t="n">
-        <v>89671</v>
+        <v>89181</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8488,21 +8488,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>937</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317054</v>
+        <v>317131</v>
       </c>
       <c r="R61" t="n">
-        <v>6566709</v>
+        <v>6566427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8569,22 +8569,22 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113336300</v>
+        <v>113335725</v>
       </c>
       <c r="B62" t="n">
-        <v>90021</v>
+        <v>89674</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3242</v>
+        <v>937</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317034</v>
+        <v>317054</v>
       </c>
       <c r="R62" t="n">
-        <v>6566659</v>
+        <v>6566709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8704,17 +8704,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
         <v>113335903</v>
       </c>
       <c r="B63" t="n">
-        <v>91545</v>
+        <v>91550</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113335687</v>
+        <v>113336300</v>
       </c>
       <c r="B64" t="n">
-        <v>89178</v>
+        <v>90024</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317131</v>
+        <v>317034</v>
       </c>
       <c r="R64" t="n">
-        <v>6566427</v>
+        <v>6566659</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B65" t="n">
-        <v>78171</v>
+        <v>56001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,34 +9004,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9039,10 +9048,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R65" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9083,28 +9092,12 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9122,10 +9115,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338164</v>
+        <v>113338079</v>
       </c>
       <c r="B66" t="n">
-        <v>55999</v>
+        <v>56782</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9134,41 +9127,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9178,10 +9163,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317128</v>
+        <v>317148</v>
       </c>
       <c r="R66" t="n">
-        <v>6566863</v>
+        <v>6566451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9228,6 +9213,21 @@
       <c r="AI66" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338079</v>
+        <v>113338739</v>
       </c>
       <c r="B67" t="n">
-        <v>56780</v>
+        <v>78173</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9261,31 +9261,30 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9293,10 +9292,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317148</v>
+        <v>317102</v>
       </c>
       <c r="R67" t="n">
-        <v>6566451</v>
+        <v>6566586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9337,27 +9336,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378820</v>
+        <v>113378352</v>
       </c>
       <c r="B68" t="n">
-        <v>94921</v>
+        <v>5163</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,31 +9391,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9426,7 +9427,7 @@
         <v>316796</v>
       </c>
       <c r="R68" t="n">
-        <v>6567088</v>
+        <v>6566783</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9470,6 +9471,26 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Torrgren på låga # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9486,10 +9507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378087</v>
+        <v>113377913</v>
       </c>
       <c r="B69" t="n">
-        <v>90701</v>
+        <v>94926</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9502,30 +9523,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5454</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9533,10 +9555,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316719</v>
+        <v>316859</v>
       </c>
       <c r="R69" t="n">
-        <v>6566788</v>
+        <v>6566682</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9588,17 +9610,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9616,10 +9638,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378411</v>
+        <v>113378172</v>
       </c>
       <c r="B70" t="n">
-        <v>4990</v>
+        <v>89674</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9632,32 +9654,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105212</v>
+        <v>937</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9665,10 +9685,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316861</v>
+        <v>316763</v>
       </c>
       <c r="R70" t="n">
-        <v>6566893</v>
+        <v>6566812</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9720,17 +9740,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9748,10 +9768,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378364</v>
+        <v>113378087</v>
       </c>
       <c r="B71" t="n">
-        <v>94921</v>
+        <v>90706</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9764,31 +9784,30 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>5454</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9796,10 +9815,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316813</v>
+        <v>316719</v>
       </c>
       <c r="R71" t="n">
-        <v>6566808</v>
+        <v>6566788</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9879,10 +9898,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113378172</v>
+        <v>113378035</v>
       </c>
       <c r="B72" t="n">
-        <v>89671</v>
+        <v>94926</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9895,30 +9914,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9926,10 +9946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316763</v>
+        <v>316688</v>
       </c>
       <c r="R72" t="n">
-        <v>6566812</v>
+        <v>6566808</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9981,17 +10001,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10009,10 +10029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113378352</v>
+        <v>113377981</v>
       </c>
       <c r="B73" t="n">
-        <v>5163</v>
+        <v>90359</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10025,32 +10045,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102204</v>
+        <v>73</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10058,10 +10076,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316796</v>
+        <v>316671</v>
       </c>
       <c r="R73" t="n">
-        <v>6566783</v>
+        <v>6566772</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10113,17 +10131,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10141,10 +10159,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113377913</v>
+        <v>113378774</v>
       </c>
       <c r="B74" t="n">
-        <v>94921</v>
+        <v>94926</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10189,10 +10207,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316859</v>
+        <v>316837</v>
       </c>
       <c r="R74" t="n">
-        <v>6566682</v>
+        <v>6566820</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10244,17 +10262,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10272,10 +10290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378774</v>
+        <v>113378820</v>
       </c>
       <c r="B75" t="n">
-        <v>94921</v>
+        <v>94926</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10320,10 +10338,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316837</v>
+        <v>316796</v>
       </c>
       <c r="R75" t="n">
-        <v>6566820</v>
+        <v>6567088</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10367,26 +10385,6 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10403,10 +10401,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113377981</v>
+        <v>113378411</v>
       </c>
       <c r="B76" t="n">
-        <v>90356</v>
+        <v>4990</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10419,30 +10417,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>105212</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316671</v>
+        <v>316861</v>
       </c>
       <c r="R76" t="n">
-        <v>6566772</v>
+        <v>6566893</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10505,17 +10505,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10536,7 +10536,7 @@
         <v>113378715</v>
       </c>
       <c r="B77" t="n">
-        <v>90315</v>
+        <v>90318</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10663,10 +10663,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113377902</v>
+        <v>113378364</v>
       </c>
       <c r="B78" t="n">
-        <v>94921</v>
+        <v>94926</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316879</v>
+        <v>316813</v>
       </c>
       <c r="R78" t="n">
-        <v>6566606</v>
+        <v>6566808</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10794,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378035</v>
+        <v>113377902</v>
       </c>
       <c r="B79" t="n">
-        <v>94921</v>
+        <v>94926</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316688</v>
+        <v>316879</v>
       </c>
       <c r="R79" t="n">
-        <v>6566808</v>
+        <v>6566606</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90315</v>
+        <v>90318</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113405650</v>
+        <v>113427239</v>
       </c>
       <c r="B81" t="n">
-        <v>43548</v>
+        <v>90560</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11067,36 +11067,34 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>101735</v>
+        <v>5467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11104,10 +11102,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316574</v>
+        <v>316795</v>
       </c>
       <c r="R81" t="n">
-        <v>6566830</v>
+        <v>6567015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11134,12 +11132,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11154,22 +11152,22 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11187,10 +11185,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113427239</v>
+        <v>113405679</v>
       </c>
       <c r="B82" t="n">
-        <v>90555</v>
+        <v>43550</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11199,34 +11197,36 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5467</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316795</v>
+        <v>316567</v>
       </c>
       <c r="R82" t="n">
-        <v>6567015</v>
+        <v>6566848</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11264,12 +11264,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11284,22 +11284,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113405679</v>
+        <v>113406315</v>
       </c>
       <c r="B83" t="n">
-        <v>43548</v>
+        <v>90024</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11329,36 +11329,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11366,10 +11368,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316567</v>
+        <v>316935</v>
       </c>
       <c r="R83" t="n">
-        <v>6566848</v>
+        <v>6566886</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11416,22 +11418,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11449,10 +11451,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427288</v>
+        <v>113427359</v>
       </c>
       <c r="B84" t="n">
-        <v>90315</v>
+        <v>94926</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11461,34 +11463,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5260</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11496,10 +11499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316863</v>
+        <v>316843</v>
       </c>
       <c r="R84" t="n">
-        <v>6567163</v>
+        <v>6567130</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11579,10 +11582,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427359</v>
+        <v>113427288</v>
       </c>
       <c r="B85" t="n">
-        <v>94921</v>
+        <v>90318</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11591,35 +11594,34 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11627,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316843</v>
+        <v>316863</v>
       </c>
       <c r="R85" t="n">
-        <v>6567130</v>
+        <v>6567163</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11710,10 +11712,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113406315</v>
+        <v>113405650</v>
       </c>
       <c r="B86" t="n">
-        <v>90021</v>
+        <v>43550</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11722,38 +11724,36 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316935</v>
+        <v>316574</v>
       </c>
       <c r="R86" t="n">
-        <v>6566886</v>
+        <v>6566830</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11811,22 +11811,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12477,7 +12477,7 @@
         <v>113335584</v>
       </c>
       <c r="B92" t="n">
-        <v>90543</v>
+        <v>90548</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90498</v>
+        <v>90503</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -8992,10 +8992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113338164</v>
+        <v>113338079</v>
       </c>
       <c r="B65" t="n">
-        <v>56001</v>
+        <v>56810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9004,41 +9004,33 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9048,10 +9040,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317128</v>
+        <v>317148</v>
       </c>
       <c r="R65" t="n">
-        <v>6566863</v>
+        <v>6566451</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9098,6 +9090,21 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Barrblandingsskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9115,10 +9122,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113338079</v>
+        <v>113338739</v>
       </c>
       <c r="B66" t="n">
-        <v>56782</v>
+        <v>78201</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9131,31 +9138,30 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9163,10 +9169,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317148</v>
+        <v>317102</v>
       </c>
       <c r="R66" t="n">
-        <v>6566451</v>
+        <v>6566586</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9207,27 +9213,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrblandingsskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Torrkvist # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9245,10 +9252,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113338739</v>
+        <v>113338164</v>
       </c>
       <c r="B67" t="n">
-        <v>78173</v>
+        <v>56029</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9257,34 +9264,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9292,10 +9308,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317102</v>
+        <v>317128</v>
       </c>
       <c r="R67" t="n">
-        <v>6566586</v>
+        <v>6566863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9336,28 +9352,12 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Torrkvist # Picea abies</t>
+          <t>Barrblandingsskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378352</v>
+        <v>113378087</v>
       </c>
       <c r="B68" t="n">
-        <v>5163</v>
+        <v>90737</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,32 +9391,30 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102204</v>
+        <v>5454</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9424,10 +9422,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316796</v>
+        <v>316719</v>
       </c>
       <c r="R68" t="n">
-        <v>6566783</v>
+        <v>6566788</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9479,17 +9477,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9507,10 +9505,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113377913</v>
+        <v>113378035</v>
       </c>
       <c r="B69" t="n">
-        <v>94926</v>
+        <v>94954</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9555,10 +9553,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316859</v>
+        <v>316688</v>
       </c>
       <c r="R69" t="n">
-        <v>6566682</v>
+        <v>6566808</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9610,17 +9608,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9638,10 +9636,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378172</v>
+        <v>113378774</v>
       </c>
       <c r="B70" t="n">
-        <v>89674</v>
+        <v>94954</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9654,30 +9652,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9685,10 +9684,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316763</v>
+        <v>316837</v>
       </c>
       <c r="R70" t="n">
-        <v>6566812</v>
+        <v>6566820</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9740,17 +9739,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9768,10 +9767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378087</v>
+        <v>113378172</v>
       </c>
       <c r="B71" t="n">
-        <v>90706</v>
+        <v>89702</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9784,21 +9783,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5454</v>
+        <v>937</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9815,10 +9814,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316719</v>
+        <v>316763</v>
       </c>
       <c r="R71" t="n">
-        <v>6566788</v>
+        <v>6566812</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9870,17 +9869,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9898,10 +9897,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113378035</v>
+        <v>113378411</v>
       </c>
       <c r="B72" t="n">
-        <v>94926</v>
+        <v>4990</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9914,31 +9913,32 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>105212</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316688</v>
+        <v>316861</v>
       </c>
       <c r="R72" t="n">
-        <v>6566808</v>
+        <v>6566893</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10001,17 +10001,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10029,10 +10029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113377981</v>
+        <v>113377913</v>
       </c>
       <c r="B73" t="n">
-        <v>90359</v>
+        <v>94954</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10045,30 +10045,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10076,10 +10077,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316671</v>
+        <v>316859</v>
       </c>
       <c r="R73" t="n">
-        <v>6566772</v>
+        <v>6566682</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10131,17 +10132,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10159,10 +10160,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378774</v>
+        <v>113378715</v>
       </c>
       <c r="B74" t="n">
-        <v>94926</v>
+        <v>90349</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10171,35 +10172,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10207,10 +10207,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316837</v>
+        <v>316843</v>
       </c>
       <c r="R74" t="n">
-        <v>6566820</v>
+        <v>6567058</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10290,10 +10290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113378820</v>
+        <v>113377902</v>
       </c>
       <c r="B75" t="n">
-        <v>94926</v>
+        <v>94954</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10338,10 +10338,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316796</v>
+        <v>316879</v>
       </c>
       <c r="R75" t="n">
-        <v>6567088</v>
+        <v>6566606</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10385,6 +10385,26 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -10401,10 +10421,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378411</v>
+        <v>113378820</v>
       </c>
       <c r="B76" t="n">
-        <v>4990</v>
+        <v>94954</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10417,32 +10437,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105212</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10450,10 +10469,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316861</v>
+        <v>316796</v>
       </c>
       <c r="R76" t="n">
-        <v>6566893</v>
+        <v>6567088</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10497,26 +10516,6 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Ståande torrträd # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10533,10 +10532,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113378715</v>
+        <v>113377981</v>
       </c>
       <c r="B77" t="n">
-        <v>90318</v>
+        <v>90390</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10545,25 +10544,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5260</v>
+        <v>73</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10580,10 +10579,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316843</v>
+        <v>316671</v>
       </c>
       <c r="R77" t="n">
-        <v>6567058</v>
+        <v>6566772</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10635,17 +10634,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10666,7 +10665,7 @@
         <v>113378364</v>
       </c>
       <c r="B78" t="n">
-        <v>94926</v>
+        <v>94954</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10794,10 +10793,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113377902</v>
+        <v>113378352</v>
       </c>
       <c r="B79" t="n">
-        <v>94926</v>
+        <v>5163</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10810,31 +10809,32 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316879</v>
+        <v>316796</v>
       </c>
       <c r="R79" t="n">
-        <v>6566606</v>
+        <v>6566783</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10897,17 +10897,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90318</v>
+        <v>90349</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427239</v>
+        <v>113427359</v>
       </c>
       <c r="B81" t="n">
-        <v>90560</v>
+        <v>94954</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11071,30 +11071,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5467</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11102,10 +11103,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316795</v>
+        <v>316843</v>
       </c>
       <c r="R81" t="n">
-        <v>6567015</v>
+        <v>6567130</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11188,7 +11189,7 @@
         <v>113405679</v>
       </c>
       <c r="B82" t="n">
-        <v>43550</v>
+        <v>43577</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11317,10 +11318,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113406315</v>
+        <v>113427288</v>
       </c>
       <c r="B83" t="n">
-        <v>90024</v>
+        <v>90349</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11329,32 +11330,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3242</v>
+        <v>5260</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11368,10 +11365,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316935</v>
+        <v>316863</v>
       </c>
       <c r="R83" t="n">
-        <v>6566886</v>
+        <v>6567163</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11398,12 +11395,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11418,7 +11415,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11433,7 +11430,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11451,10 +11448,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427359</v>
+        <v>113406315</v>
       </c>
       <c r="B84" t="n">
-        <v>94926</v>
+        <v>90055</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11467,31 +11464,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316843</v>
+        <v>316935</v>
       </c>
       <c r="R84" t="n">
-        <v>6567130</v>
+        <v>6566886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427288</v>
+        <v>113427239</v>
       </c>
       <c r="B85" t="n">
-        <v>90318</v>
+        <v>90591</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11594,25 +11594,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5260</v>
+        <v>5467</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316863</v>
+        <v>316795</v>
       </c>
       <c r="R85" t="n">
-        <v>6567163</v>
+        <v>6567015</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
         <v>113405650</v>
       </c>
       <c r="B86" t="n">
-        <v>43550</v>
+        <v>43577</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>113338219</v>
       </c>
       <c r="B93" t="n">
-        <v>90503</v>
+        <v>90534</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -9767,10 +9767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378172</v>
+        <v>113378411</v>
       </c>
       <c r="B71" t="n">
-        <v>89702</v>
+        <v>4990</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9783,30 +9783,32 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>937</v>
+        <v>105212</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9814,10 +9816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316763</v>
+        <v>316861</v>
       </c>
       <c r="R71" t="n">
-        <v>6566812</v>
+        <v>6566893</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9869,17 +9871,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9897,10 +9899,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113378411</v>
+        <v>113378172</v>
       </c>
       <c r="B72" t="n">
-        <v>4990</v>
+        <v>89702</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9913,32 +9915,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105212</v>
+        <v>937</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316861</v>
+        <v>316763</v>
       </c>
       <c r="R72" t="n">
-        <v>6566893</v>
+        <v>6566812</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10001,17 +10001,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -9375,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113378087</v>
+        <v>113378411</v>
       </c>
       <c r="B68" t="n">
-        <v>90737</v>
+        <v>4990</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9391,30 +9391,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5454</v>
+        <v>105212</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9422,10 +9424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>316719</v>
+        <v>316861</v>
       </c>
       <c r="R68" t="n">
-        <v>6566788</v>
+        <v>6566893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9477,17 +9479,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Ståande torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9505,10 +9507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113378035</v>
+        <v>113377981</v>
       </c>
       <c r="B69" t="n">
-        <v>94954</v>
+        <v>90391</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9521,31 +9523,30 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9553,10 +9554,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>316688</v>
+        <v>316671</v>
       </c>
       <c r="R69" t="n">
-        <v>6566808</v>
+        <v>6566772</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9608,17 +9609,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9636,7 +9637,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113378774</v>
+        <v>113377902</v>
       </c>
       <c r="B70" t="n">
         <v>94954</v>
@@ -9684,10 +9685,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>316837</v>
+        <v>316879</v>
       </c>
       <c r="R70" t="n">
-        <v>6566820</v>
+        <v>6566606</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9767,10 +9768,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113378411</v>
+        <v>113378172</v>
       </c>
       <c r="B71" t="n">
-        <v>4990</v>
+        <v>89702</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9783,32 +9784,30 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105212</v>
+        <v>937</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9816,10 +9815,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>316861</v>
+        <v>316763</v>
       </c>
       <c r="R71" t="n">
-        <v>6566893</v>
+        <v>6566812</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9871,17 +9870,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Ståande torrträd # Picea abies</t>
+          <t>Låga # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9899,10 +9898,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113378172</v>
+        <v>113378820</v>
       </c>
       <c r="B72" t="n">
-        <v>89702</v>
+        <v>94954</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9915,30 +9914,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>316763</v>
+        <v>316796</v>
       </c>
       <c r="R72" t="n">
-        <v>6566812</v>
+        <v>6567088</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9993,26 +9993,6 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -10029,7 +10009,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113377913</v>
+        <v>113378774</v>
       </c>
       <c r="B73" t="n">
         <v>94954</v>
@@ -10077,10 +10057,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>316859</v>
+        <v>316837</v>
       </c>
       <c r="R73" t="n">
-        <v>6566682</v>
+        <v>6566820</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10132,17 +10112,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10160,10 +10140,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113378715</v>
+        <v>113378087</v>
       </c>
       <c r="B74" t="n">
-        <v>90349</v>
+        <v>90738</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10172,25 +10152,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5260</v>
+        <v>5454</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10207,10 +10187,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>316843</v>
+        <v>316719</v>
       </c>
       <c r="R74" t="n">
-        <v>6567058</v>
+        <v>6566788</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10272,7 +10252,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10290,7 +10270,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113377902</v>
+        <v>113378364</v>
       </c>
       <c r="B75" t="n">
         <v>94954</v>
@@ -10338,10 +10318,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>316879</v>
+        <v>316813</v>
       </c>
       <c r="R75" t="n">
-        <v>6566606</v>
+        <v>6566808</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10421,10 +10401,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113378820</v>
+        <v>113378715</v>
       </c>
       <c r="B76" t="n">
-        <v>94954</v>
+        <v>90350</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10433,35 +10413,34 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>5260</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10469,10 +10448,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>316796</v>
+        <v>316843</v>
       </c>
       <c r="R76" t="n">
-        <v>6567088</v>
+        <v>6567058</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10516,6 +10495,26 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10532,10 +10531,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113377981</v>
+        <v>113377913</v>
       </c>
       <c r="B77" t="n">
-        <v>90390</v>
+        <v>94954</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10548,30 +10547,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>316671</v>
+        <v>316859</v>
       </c>
       <c r="R77" t="n">
-        <v>6566772</v>
+        <v>6566682</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10634,17 +10634,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10662,10 +10662,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113378364</v>
+        <v>113378352</v>
       </c>
       <c r="B78" t="n">
-        <v>94954</v>
+        <v>5163</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10678,31 +10678,32 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10710,10 +10711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>316813</v>
+        <v>316796</v>
       </c>
       <c r="R78" t="n">
-        <v>6566808</v>
+        <v>6566783</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10765,17 +10766,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Torrgren på låga # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10793,10 +10794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113378352</v>
+        <v>113378035</v>
       </c>
       <c r="B79" t="n">
-        <v>5163</v>
+        <v>94954</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10809,32 +10810,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102204</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>316796</v>
+        <v>316688</v>
       </c>
       <c r="R79" t="n">
-        <v>6566783</v>
+        <v>6566808</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10897,17 +10897,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Torrgren på låga # Picea abies</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
         <v>113378726</v>
       </c>
       <c r="B80" t="n">
-        <v>90349</v>
+        <v>90350</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113427359</v>
+        <v>113427239</v>
       </c>
       <c r="B81" t="n">
-        <v>94954</v>
+        <v>90592</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11071,31 +11071,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>5467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11103,10 +11102,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>316843</v>
+        <v>316795</v>
       </c>
       <c r="R81" t="n">
-        <v>6567130</v>
+        <v>6567015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11318,10 +11317,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113427288</v>
+        <v>113405650</v>
       </c>
       <c r="B83" t="n">
-        <v>90349</v>
+        <v>43577</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11330,34 +11329,36 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11365,10 +11366,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316863</v>
+        <v>316574</v>
       </c>
       <c r="R83" t="n">
-        <v>6567163</v>
+        <v>6566830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11395,12 +11396,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11415,22 +11416,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11448,10 +11449,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113406315</v>
+        <v>113427288</v>
       </c>
       <c r="B84" t="n">
-        <v>90055</v>
+        <v>90350</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11460,32 +11461,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3242</v>
+        <v>5260</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11499,10 +11496,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316935</v>
+        <v>316863</v>
       </c>
       <c r="R84" t="n">
-        <v>6566886</v>
+        <v>6567163</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11529,12 +11526,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11549,7 +11546,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11564,7 +11561,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11582,10 +11579,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113427239</v>
+        <v>113406315</v>
       </c>
       <c r="B85" t="n">
-        <v>90591</v>
+        <v>90056</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11598,24 +11595,28 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5467</v>
+        <v>3242</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -11629,10 +11630,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316795</v>
+        <v>316935</v>
       </c>
       <c r="R85" t="n">
-        <v>6567015</v>
+        <v>6566886</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11659,12 +11660,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11679,7 +11680,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -11694,7 +11695,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11712,10 +11713,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113405650</v>
+        <v>113427359</v>
       </c>
       <c r="B86" t="n">
-        <v>43577</v>
+        <v>94954</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11724,36 +11725,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316574</v>
+        <v>316843</v>
       </c>
       <c r="R86" t="n">
-        <v>6566830</v>
+        <v>6567130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11791,12 +11791,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11811,22 +11811,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11058,7 +11058,7 @@
         <v>113427239</v>
       </c>
       <c r="B81" t="n">
-        <v>90592</v>
+        <v>90596</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113405679</v>
+        <v>113427288</v>
       </c>
       <c r="B82" t="n">
-        <v>43577</v>
+        <v>90354</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11197,36 +11197,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>5260</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11234,10 +11232,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>316567</v>
+        <v>316863</v>
       </c>
       <c r="R82" t="n">
-        <v>6566848</v>
+        <v>6567163</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11264,12 +11262,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11284,22 +11282,22 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11317,10 +11315,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113405650</v>
+        <v>113427359</v>
       </c>
       <c r="B83" t="n">
-        <v>43577</v>
+        <v>94958</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11329,36 +11327,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11366,10 +11363,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>316574</v>
+        <v>316843</v>
       </c>
       <c r="R83" t="n">
-        <v>6566830</v>
+        <v>6567130</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11396,12 +11393,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11416,22 +11413,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bär-ljung-barrblanskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Betula pubescens subsp. pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11449,10 +11446,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113427288</v>
+        <v>113405650</v>
       </c>
       <c r="B84" t="n">
-        <v>90350</v>
+        <v>43577</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11461,34 +11458,36 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11496,10 +11495,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>316863</v>
+        <v>316574</v>
       </c>
       <c r="R84" t="n">
-        <v>6567163</v>
+        <v>6566830</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11526,12 +11525,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11546,22 +11545,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11579,10 +11578,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113406315</v>
+        <v>113405679</v>
       </c>
       <c r="B85" t="n">
-        <v>90056</v>
+        <v>43577</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11591,38 +11590,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11630,10 +11627,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>316935</v>
+        <v>316567</v>
       </c>
       <c r="R85" t="n">
-        <v>6566886</v>
+        <v>6566848</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11680,22 +11677,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vanlig glasbjörk</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Högstubbe och fnöskticka # Betula pubescens subsp. pubescens</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11713,10 +11710,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113427359</v>
+        <v>113406315</v>
       </c>
       <c r="B86" t="n">
-        <v>94954</v>
+        <v>90060</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11729,31 +11726,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>316843</v>
+        <v>316935</v>
       </c>
       <c r="R86" t="n">
-        <v>6567130</v>
+        <v>6566886</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11791,12 +11791,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Bär-ljung-barrblanskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11844,10 +11844,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102962393</v>
+        <v>113670333</v>
       </c>
       <c r="B87" t="n">
-        <v>96334</v>
+        <v>94958</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11856,25 +11856,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11888,14 +11888,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norr om L. Högebergstjärnet, Dls</t>
+          <t>Öster om Byrvattnen, Dls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317253.8879412231</v>
+        <v>316786</v>
       </c>
       <c r="R87" t="n">
-        <v>6566880.994906534</v>
+        <v>6566912</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11922,22 +11922,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11952,7 +11942,22 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11970,10 +11975,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>107100461</v>
+        <v>113670354</v>
       </c>
       <c r="B88" t="n">
-        <v>43464</v>
+        <v>91582</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11982,50 +11987,48 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>101735</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lilla Högebergstjärnen N, Dls</t>
+          <t>Öster om Byrvattnen, Dls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317279.7054260897</v>
+        <v>316760</v>
       </c>
       <c r="R88" t="n">
-        <v>6566915.663342874</v>
+        <v>6566984</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12049,22 +12052,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12079,90 +12072,94 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Mosse och blåbärgranskog m löv</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>107100506</v>
+        <v>113670454</v>
       </c>
       <c r="B89" t="n">
-        <v>98520</v>
+        <v>94958</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ängemossen N/O, Dls</t>
+          <t>Öster om Byrvattnen, Dls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317169.4733760823</v>
+        <v>316994</v>
       </c>
       <c r="R89" t="n">
-        <v>6566985.079957743</v>
+        <v>6567062</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12186,22 +12183,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12216,28 +12203,43 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Mosseblandskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113245275</v>
+        <v>113671023</v>
       </c>
       <c r="B90" t="n">
-        <v>90249</v>
+        <v>97402</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12250,30 +12252,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -12281,10 +12284,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317246</v>
+        <v>317007</v>
       </c>
       <c r="R90" t="n">
-        <v>6566798</v>
+        <v>6566956</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12311,12 +12314,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12328,6 +12331,11 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12344,10 +12352,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113245353</v>
+        <v>113676316</v>
       </c>
       <c r="B91" t="n">
-        <v>89671</v>
+        <v>56029</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12356,34 +12364,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>937</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12391,10 +12396,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317172</v>
+        <v>317023</v>
       </c>
       <c r="R91" t="n">
-        <v>6566905</v>
+        <v>6566938</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12421,12 +12426,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Betestallar med spillning under</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12435,28 +12445,27 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Betesträd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12474,10 +12483,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113335584</v>
+        <v>113651540</v>
       </c>
       <c r="B92" t="n">
-        <v>90548</v>
+        <v>94958</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12490,30 +12499,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1213</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12521,10 +12531,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317269</v>
+        <v>316757</v>
       </c>
       <c r="R92" t="n">
-        <v>6566835</v>
+        <v>6566979</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12551,12 +12561,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12571,7 +12581,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12586,7 +12596,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12604,10 +12614,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>113338219</v>
+        <v>113670219</v>
       </c>
       <c r="B93" t="n">
-        <v>90534</v>
+        <v>91582</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12616,25 +12626,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5321</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12651,10 +12661,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317173</v>
+        <v>316716</v>
       </c>
       <c r="R93" t="n">
-        <v>6566926</v>
+        <v>6566805</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12681,12 +12691,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12701,22 +12711,22 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12731,6 +12741,1398 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>113670749</v>
+      </c>
+      <c r="B94" t="n">
+        <v>97402</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>317013</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6567032</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>113670615</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94958</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>53</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>317055</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6567039</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>113676622</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>316692</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6566746</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>113683299</v>
+      </c>
+      <c r="B97" t="n">
+        <v>90828</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>250072</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Erastia ochraceolateritia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Bondartsev) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>316977</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6567021</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Låg med markkontakt # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>102962393</v>
+      </c>
+      <c r="B98" t="n">
+        <v>96334</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Norr om L. Högebergstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>317253.8879412231</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6566880.994906534</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>107100461</v>
+      </c>
+      <c r="B99" t="n">
+        <v>43464</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lilla Högebergstjärnen N, Dls</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>317279.7054260897</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6566915.663342874</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Mosse och blåbärgranskog m löv</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Tommy Solberg, Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>107100506</v>
+      </c>
+      <c r="B100" t="n">
+        <v>98520</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ängemossen N/O, Dls</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>317169.4733760823</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6566985.079957743</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Mosseblandskog</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Tommy Solberg, Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>113245275</v>
+      </c>
+      <c r="B101" t="n">
+        <v>90249</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>317246</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6566798</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>113245353</v>
+      </c>
+      <c r="B102" t="n">
+        <v>89671</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>937</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>317172</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6566905</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>113335584</v>
+      </c>
+      <c r="B103" t="n">
+        <v>90548</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1213</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knölgrynna</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phlebia femsjoeensis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>317269</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6566835</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>113338219</v>
+      </c>
+      <c r="B104" t="n">
+        <v>90534</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Rigidoporus corticola</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>317173</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6566926</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -11844,10 +11844,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113670333</v>
+        <v>113676622</v>
       </c>
       <c r="B87" t="n">
-        <v>94958</v>
+        <v>78201</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11860,31 +11860,30 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11892,10 +11891,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316786</v>
+        <v>316692</v>
       </c>
       <c r="R87" t="n">
-        <v>6566912</v>
+        <v>6566746</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11957,7 +11956,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11975,10 +11974,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113670354</v>
+        <v>113670615</v>
       </c>
       <c r="B88" t="n">
-        <v>91582</v>
+        <v>94958</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11991,30 +11990,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -12022,10 +12022,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>316760</v>
+        <v>317055</v>
       </c>
       <c r="R88" t="n">
-        <v>6566984</v>
+        <v>6567039</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12236,10 +12236,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113671023</v>
+        <v>113670219</v>
       </c>
       <c r="B90" t="n">
-        <v>97402</v>
+        <v>91582</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12248,35 +12248,34 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -12284,10 +12283,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317007</v>
+        <v>316716</v>
       </c>
       <c r="R90" t="n">
-        <v>6566956</v>
+        <v>6566805</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12334,7 +12333,22 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12352,10 +12366,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113676316</v>
+        <v>113670354</v>
       </c>
       <c r="B91" t="n">
-        <v>56029</v>
+        <v>91582</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12364,31 +12378,34 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12396,10 +12413,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317023</v>
+        <v>316760</v>
       </c>
       <c r="R91" t="n">
-        <v>6566938</v>
+        <v>6566984</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12434,17 +12451,13 @@
           <t>2023-12-18</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Betestallar med spillning under</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12465,7 +12478,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Betesträd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12483,10 +12496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113651540</v>
+        <v>113670749</v>
       </c>
       <c r="B92" t="n">
-        <v>94958</v>
+        <v>97402</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12495,25 +12508,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12531,10 +12544,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>316757</v>
+        <v>317013</v>
       </c>
       <c r="R92" t="n">
-        <v>6566979</v>
+        <v>6567032</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12561,12 +12574,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-12-16</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-12-16</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12582,21 +12595,6 @@
       <c r="AI92" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12614,10 +12612,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>113670219</v>
+        <v>113670333</v>
       </c>
       <c r="B93" t="n">
-        <v>91582</v>
+        <v>94958</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12630,30 +12628,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12661,10 +12660,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>316716</v>
+        <v>316786</v>
       </c>
       <c r="R93" t="n">
-        <v>6566805</v>
+        <v>6566912</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12711,7 +12710,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -12744,7 +12743,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>113670749</v>
+        <v>113671023</v>
       </c>
       <c r="B94" t="n">
         <v>97402</v>
@@ -12792,10 +12791,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317013</v>
+        <v>317007</v>
       </c>
       <c r="R94" t="n">
-        <v>6567032</v>
+        <v>6566956</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12860,7 +12859,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>113670615</v>
+        <v>113651540</v>
       </c>
       <c r="B95" t="n">
         <v>94958</v>
@@ -12908,10 +12907,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317055</v>
+        <v>316757</v>
       </c>
       <c r="R95" t="n">
-        <v>6567039</v>
+        <v>6566979</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12938,12 +12937,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12991,10 +12990,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>113676622</v>
+        <v>113676316</v>
       </c>
       <c r="B96" t="n">
-        <v>78201</v>
+        <v>56029</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13003,34 +13002,31 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -13038,10 +13034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>316692</v>
+        <v>317023</v>
       </c>
       <c r="R96" t="n">
-        <v>6566746</v>
+        <v>6566938</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13076,13 +13072,17 @@
           <t>2023-12-18</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Betestallar med spillning under</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Levande träd # Pinus sylvestris</t>
+          <t>Betesträd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -11844,10 +11844,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113676622</v>
+        <v>113670354</v>
       </c>
       <c r="B87" t="n">
-        <v>78201</v>
+        <v>91582</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11860,27 +11860,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -11891,10 +11891,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316692</v>
+        <v>316760</v>
       </c>
       <c r="R87" t="n">
-        <v>6566746</v>
+        <v>6566984</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Levande träd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11974,7 +11974,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113670615</v>
+        <v>113670333</v>
       </c>
       <c r="B88" t="n">
         <v>94958</v>
@@ -12022,10 +12022,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317055</v>
+        <v>316786</v>
       </c>
       <c r="R88" t="n">
-        <v>6567039</v>
+        <v>6566912</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12105,10 +12105,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113670454</v>
+        <v>113670219</v>
       </c>
       <c r="B89" t="n">
-        <v>94958</v>
+        <v>91582</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12121,31 +12121,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12153,10 +12152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>316994</v>
+        <v>316716</v>
       </c>
       <c r="R89" t="n">
-        <v>6567062</v>
+        <v>6566805</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12203,7 +12202,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12236,10 +12235,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113670219</v>
+        <v>113670749</v>
       </c>
       <c r="B90" t="n">
-        <v>91582</v>
+        <v>97402</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12248,34 +12247,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>316716</v>
+        <v>317013</v>
       </c>
       <c r="R90" t="n">
-        <v>6566805</v>
+        <v>6567032</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12333,22 +12333,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12366,10 +12351,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113670354</v>
+        <v>113676622</v>
       </c>
       <c r="B91" t="n">
-        <v>91582</v>
+        <v>78201</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12382,27 +12367,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -12413,10 +12398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316760</v>
+        <v>316692</v>
       </c>
       <c r="R91" t="n">
-        <v>6566984</v>
+        <v>6566746</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12478,7 +12463,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12496,10 +12481,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113670749</v>
+        <v>113670615</v>
       </c>
       <c r="B92" t="n">
-        <v>97402</v>
+        <v>94958</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12508,25 +12493,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12544,10 +12529,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317013</v>
+        <v>317055</v>
       </c>
       <c r="R92" t="n">
-        <v>6567032</v>
+        <v>6567039</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12595,6 +12580,21 @@
       <c r="AI92" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12612,10 +12612,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>113670333</v>
+        <v>113671023</v>
       </c>
       <c r="B93" t="n">
-        <v>94958</v>
+        <v>97402</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12624,25 +12624,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>316786</v>
+        <v>317007</v>
       </c>
       <c r="R93" t="n">
-        <v>6566912</v>
+        <v>6566956</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12711,21 +12711,6 @@
       <c r="AI93" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12743,10 +12728,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>113671023</v>
+        <v>113670454</v>
       </c>
       <c r="B94" t="n">
-        <v>97402</v>
+        <v>94958</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12755,25 +12740,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12791,10 +12776,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317007</v>
+        <v>316994</v>
       </c>
       <c r="R94" t="n">
-        <v>6566956</v>
+        <v>6567062</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12842,6 +12827,21 @@
       <c r="AI94" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12990,10 +12990,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>113676316</v>
+        <v>113683299</v>
       </c>
       <c r="B96" t="n">
-        <v>56029</v>
+        <v>90828</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13002,31 +13002,29 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>250072</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Erastia ochraceolateritia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bondartsev) Zmitr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -13034,10 +13032,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>317023</v>
+        <v>316977</v>
       </c>
       <c r="R96" t="n">
-        <v>6566938</v>
+        <v>6567021</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13072,23 +13070,19 @@
           <t>2023-12-18</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Betestallar med spillning under</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13103,7 +13097,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Betesträd # Pinus sylvestris</t>
+          <t>Låg med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13121,10 +13115,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>113683299</v>
+        <v>113676316</v>
       </c>
       <c r="B97" t="n">
-        <v>90828</v>
+        <v>56029</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13133,29 +13127,31 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>250072</v>
+        <v>100138</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Erastia ochraceolateritia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Bondartsev) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -13163,10 +13159,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>316977</v>
+        <v>317023</v>
       </c>
       <c r="R97" t="n">
-        <v>6567021</v>
+        <v>6566938</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13201,19 +13197,23 @@
           <t>2023-12-18</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Betestallar med spillning under</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Låg med markkontakt # Pinus sylvestris</t>
+          <t>Betesträd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -11844,10 +11844,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113670354</v>
+        <v>113670615</v>
       </c>
       <c r="B87" t="n">
-        <v>91582</v>
+        <v>94958</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11860,30 +11860,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11891,10 +11892,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>316760</v>
+        <v>317055</v>
       </c>
       <c r="R87" t="n">
-        <v>6566984</v>
+        <v>6567039</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11974,10 +11975,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113670333</v>
+        <v>113671023</v>
       </c>
       <c r="B88" t="n">
-        <v>94958</v>
+        <v>97402</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11986,25 +11987,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12022,10 +12023,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>316786</v>
+        <v>317007</v>
       </c>
       <c r="R88" t="n">
-        <v>6566912</v>
+        <v>6566956</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12073,21 +12074,6 @@
       <c r="AI88" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12105,10 +12091,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113670219</v>
+        <v>113670749</v>
       </c>
       <c r="B89" t="n">
-        <v>91582</v>
+        <v>97402</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12117,34 +12103,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12152,10 +12139,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>316716</v>
+        <v>317013</v>
       </c>
       <c r="R89" t="n">
-        <v>6566805</v>
+        <v>6567032</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12202,22 +12189,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12235,10 +12207,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113670749</v>
+        <v>113651540</v>
       </c>
       <c r="B90" t="n">
-        <v>97402</v>
+        <v>94958</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12247,25 +12219,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12283,10 +12255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317013</v>
+        <v>316757</v>
       </c>
       <c r="R90" t="n">
-        <v>6567032</v>
+        <v>6566979</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12313,12 +12285,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12334,6 +12306,21 @@
       <c r="AI90" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12351,10 +12338,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113676622</v>
+        <v>113670354</v>
       </c>
       <c r="B91" t="n">
-        <v>78201</v>
+        <v>91582</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12367,27 +12354,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -12398,10 +12385,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316692</v>
+        <v>316760</v>
       </c>
       <c r="R91" t="n">
-        <v>6566746</v>
+        <v>6566984</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12463,7 +12450,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Levande träd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12481,10 +12468,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113670615</v>
+        <v>113676622</v>
       </c>
       <c r="B92" t="n">
-        <v>94958</v>
+        <v>78201</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12497,31 +12484,30 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12529,10 +12515,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317055</v>
+        <v>316692</v>
       </c>
       <c r="R92" t="n">
-        <v>6567039</v>
+        <v>6566746</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12594,7 +12580,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12612,10 +12598,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>113671023</v>
+        <v>113670333</v>
       </c>
       <c r="B93" t="n">
-        <v>97402</v>
+        <v>94958</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12624,25 +12610,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12660,10 +12646,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317007</v>
+        <v>316786</v>
       </c>
       <c r="R93" t="n">
-        <v>6566956</v>
+        <v>6566912</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12711,6 +12697,21 @@
       <c r="AI93" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12728,10 +12729,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>113670454</v>
+        <v>113670219</v>
       </c>
       <c r="B94" t="n">
-        <v>94958</v>
+        <v>91582</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12744,31 +12745,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316994</v>
+        <v>316716</v>
       </c>
       <c r="R94" t="n">
-        <v>6567062</v>
+        <v>6566805</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12859,7 +12859,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>113651540</v>
+        <v>113670454</v>
       </c>
       <c r="B95" t="n">
         <v>94958</v>
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316757</v>
+        <v>316994</v>
       </c>
       <c r="R95" t="n">
-        <v>6566979</v>
+        <v>6567062</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-12-16</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-12-16</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -11844,10 +11844,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113670615</v>
+        <v>113676622</v>
       </c>
       <c r="B87" t="n">
-        <v>94958</v>
+        <v>78201</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11860,31 +11860,30 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11892,10 +11891,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317055</v>
+        <v>316692</v>
       </c>
       <c r="R87" t="n">
-        <v>6567039</v>
+        <v>6566746</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11957,7 +11956,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11975,10 +11974,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113671023</v>
+        <v>113670354</v>
       </c>
       <c r="B88" t="n">
-        <v>97402</v>
+        <v>91582</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11987,35 +11986,34 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -12023,10 +12021,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317007</v>
+        <v>316760</v>
       </c>
       <c r="R88" t="n">
-        <v>6566956</v>
+        <v>6566984</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12074,6 +12072,21 @@
       <c r="AI88" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12091,7 +12104,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113670749</v>
+        <v>113671023</v>
       </c>
       <c r="B89" t="n">
         <v>97402</v>
@@ -12139,10 +12152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317013</v>
+        <v>317007</v>
       </c>
       <c r="R89" t="n">
-        <v>6567032</v>
+        <v>6566956</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12338,7 +12351,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113670354</v>
+        <v>113670219</v>
       </c>
       <c r="B91" t="n">
         <v>91582</v>
@@ -12385,10 +12398,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>316760</v>
+        <v>316716</v>
       </c>
       <c r="R91" t="n">
-        <v>6566984</v>
+        <v>6566805</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12435,7 +12448,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12468,10 +12481,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113676622</v>
+        <v>113670454</v>
       </c>
       <c r="B92" t="n">
-        <v>78201</v>
+        <v>94958</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12484,30 +12497,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12515,10 +12529,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>316692</v>
+        <v>316994</v>
       </c>
       <c r="R92" t="n">
-        <v>6566746</v>
+        <v>6567062</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12580,7 +12594,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Levande träd # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12729,10 +12743,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>113670219</v>
+        <v>113670749</v>
       </c>
       <c r="B94" t="n">
-        <v>91582</v>
+        <v>97402</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12741,34 +12755,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12776,10 +12791,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>316716</v>
+        <v>317013</v>
       </c>
       <c r="R94" t="n">
-        <v>6566805</v>
+        <v>6567032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12826,22 +12841,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12859,7 +12859,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>113670454</v>
+        <v>113670615</v>
       </c>
       <c r="B95" t="n">
         <v>94958</v>
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>316994</v>
+        <v>317055</v>
       </c>
       <c r="R95" t="n">
-        <v>6567062</v>
+        <v>6567039</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -10418,7 +10418,7 @@
         <v>113427359</v>
       </c>
       <c r="B76" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>113670454</v>
       </c>
       <c r="B81" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>113670333</v>
       </c>
       <c r="B85" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>113670615</v>
       </c>
       <c r="B87" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>113651540</v>
       </c>
       <c r="B88" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14143,10 +14143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>102962393</v>
+        <v>120194403</v>
       </c>
       <c r="B105" t="n">
-        <v>96334</v>
+        <v>91028</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14159,42 +14159,41 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1218</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitt vaxskinn</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia subulata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norr om L. Högebergstjärnet, Dls</t>
+          <t>Öster om Byrvattnen, Dls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317253.8879412231</v>
+        <v>316936</v>
       </c>
       <c r="R105" t="n">
-        <v>6566880.994906534</v>
+        <v>6567094</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14221,22 +14220,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14245,13 +14234,32 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14269,10 +14277,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>107100461</v>
+        <v>102962393</v>
       </c>
       <c r="B106" t="n">
-        <v>43464</v>
+        <v>96334</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14281,50 +14289,49 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lilla Högebergstjärnen N, Dls</t>
+          <t>Norr om L. Högebergstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>317279.7054260897</v>
+        <v>317253.8879412231</v>
       </c>
       <c r="R106" t="n">
-        <v>6566915.663342874</v>
+        <v>6566880.994906534</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14348,7 +14355,7 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
@@ -14358,7 +14365,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
@@ -14378,47 +14385,32 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Mosse och blåbärgranskog m löv</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>107100506</v>
+        <v>107100461</v>
       </c>
       <c r="B107" t="n">
-        <v>98520</v>
+        <v>43464</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14427,38 +14419,43 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ängemossen N/O, Dls</t>
+          <t>Lilla Högebergstjärnen N, Dls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317169.4733760823</v>
+        <v>317279.7054260897</v>
       </c>
       <c r="R107" t="n">
-        <v>6566985.079957743</v>
+        <v>6566915.663342874</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -14515,7 +14512,22 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Mosseblandskog</t>
+          <t>Mosse och blåbärgranskog m löv</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14533,60 +14545,57 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>113245353</v>
+        <v>107100506</v>
       </c>
       <c r="B108" t="n">
-        <v>89896</v>
+        <v>98520</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>937</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Öster om Byrvattnen, Dls</t>
+          <t>Ängemossen N/O, Dls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317172</v>
+        <v>317169.4733760823</v>
       </c>
       <c r="R108" t="n">
-        <v>6566905</v>
+        <v>6566985.079957743</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14610,12 +14619,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14630,43 +14649,28 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Låga # Populus tremula</t>
+          <t>Mosseblandskog</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Tommy Solberg, Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>113245275</v>
+        <v>113245353</v>
       </c>
       <c r="B109" t="n">
-        <v>90481</v>
+        <v>89896</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14675,25 +14679,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1503</v>
+        <v>937</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14710,10 +14714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317246</v>
+        <v>317172</v>
       </c>
       <c r="R109" t="n">
-        <v>6566798</v>
+        <v>6566905</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14757,6 +14761,26 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -14773,10 +14797,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>113335584</v>
+        <v>113245275</v>
       </c>
       <c r="B110" t="n">
-        <v>90781</v>
+        <v>90481</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14785,25 +14809,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1213</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knölgrynna</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phlebia femsjoeensis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14820,10 +14844,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317268</v>
+        <v>317246</v>
       </c>
       <c r="R110" t="n">
-        <v>6566835</v>
+        <v>6566798</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14850,12 +14874,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14867,26 +14891,6 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -14903,10 +14907,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>113338219</v>
+        <v>113335584</v>
       </c>
       <c r="B111" t="n">
-        <v>90740</v>
+        <v>90781</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14915,25 +14919,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5321</v>
+        <v>1213</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -14950,10 +14954,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317174</v>
+        <v>317268</v>
       </c>
       <c r="R111" t="n">
-        <v>6566926</v>
+        <v>6566835</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15000,22 +15004,22 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Låga # Populus tremula</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15030,6 +15034,136 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>113338219</v>
+      </c>
+      <c r="B112" t="n">
+        <v>90740</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Rigidoporus corticola</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Öster om Byrvattnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>317174</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6566926</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Låga # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 199-2023 artfynd.xlsx
+++ b/artfynd/A 199-2023 artfynd.xlsx
@@ -14146,7 +14146,7 @@
         <v>120194403</v>
       </c>
       <c r="B105" t="n">
-        <v>91028</v>
+        <v>91046</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
